--- a/data/quarterly/FY26Q2.xlsx
+++ b/data/quarterly/FY26Q2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CE5153-9DA8-AD4E-9EFD-EC02B1CCAF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490BD7D8-3A23-4342-8E84-D2A47E139A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3360" yWindow="680" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="13840" yWindow="680" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q2" sheetId="2" r:id="rId1"/>
@@ -559,12 +559,7 @@
     <cellStyle name="一般 2" xfId="2" xr:uid="{0CB5398D-811F-454E-A670-53B654D1D081}"/>
     <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1885,10 +1880,13 @@
       <c r="CD6" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="CE6" s="15">
+        <v>15</v>
+      </c>
       <c r="CF6" s="33"/>
       <c r="CG6" s="10">
         <f t="shared" si="23"/>
-        <v>-13</v>
+        <v>2</v>
       </c>
       <c r="CH6" s="12">
         <f t="shared" si="24"/>
@@ -4774,11 +4772,13 @@
       <c r="CD18" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CE18" s="15"/>
+      <c r="CE18" s="15">
+        <v>13</v>
+      </c>
       <c r="CF18" s="33"/>
       <c r="CG18" s="10">
         <f t="shared" si="23"/>
-        <v>-5</v>
+        <v>8</v>
       </c>
       <c r="CH18" s="12">
         <f t="shared" si="24"/>
@@ -7681,11 +7681,13 @@
       <c r="CD30" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CE30" s="15"/>
+      <c r="CE30" s="15">
+        <v>3</v>
+      </c>
       <c r="CF30" s="33"/>
       <c r="CG30" s="10">
         <f t="shared" si="23"/>
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CH30" s="12">
         <f t="shared" si="24"/>
@@ -10563,11 +10565,13 @@
       <c r="CD42" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CE42" s="15"/>
+      <c r="CE42" s="15">
+        <v>7</v>
+      </c>
       <c r="CF42" s="33"/>
       <c r="CG42" s="10">
         <f t="shared" si="23"/>
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="CH42" s="12">
         <f t="shared" si="24"/>
@@ -16241,6 +16245,18 @@
           <xm:sqref>BY5:CA65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{6A1FAD57-8B56-AD43-BC86-FE7B8B27DAC3}">
+            <xm:f>NOT(ISERROR(SEARCH("-",CG5)))</xm:f>
+            <xm:f>"-"</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFF0000"/>
+              </font>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>CG5:CI65</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="14" operator="containsText" id="{00C895F4-D5E3-F04E-93CB-E795A6DC8C2F}">
             <xm:f>NOT(ISERROR(SEARCH("-",CO5)))</xm:f>
             <xm:f>"-"</xm:f>
@@ -16264,18 +16280,6 @@
           </x14:cfRule>
           <xm:sqref>CW5:CY65</xm:sqref>
         </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{6A1FAD57-8B56-AD43-BC86-FE7B8B27DAC3}">
-            <xm:f>NOT(ISERROR(SEARCH("-",CG5)))</xm:f>
-            <xm:f>"-"</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFF0000"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>CG5:CI65</xm:sqref>
-        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/data/quarterly/FY26Q2.xlsx
+++ b/data/quarterly/FY26Q2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490BD7D8-3A23-4342-8E84-D2A47E139A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE836E5-63B5-A549-AD2F-CD6D457EF9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13840" yWindow="680" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="5400" yWindow="680" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="46">
   <si>
     <t>總計</t>
   </si>
@@ -228,6 +228,14 @@
   </si>
   <si>
     <t>03/08~03/14</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q2W12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03/15~03/21</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1082,7 +1090,11 @@
       </c>
       <c r="CD1" s="26"/>
       <c r="CF1" s="25"/>
-      <c r="CK1" s="26"/>
+      <c r="CK1" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="CL1" s="26"/>
+      <c r="CN1" s="25"/>
       <c r="CS1" s="26"/>
     </row>
     <row r="2" spans="1:103" s="20" customFormat="1" ht="18">
@@ -1156,7 +1168,9 @@
       <c r="CG2" s="21"/>
       <c r="CH2" s="21"/>
       <c r="CI2" s="21"/>
-      <c r="CK2" s="22"/>
+      <c r="CK2" s="20" t="s">
+        <v>45</v>
+      </c>
       <c r="CL2" s="21"/>
       <c r="CN2" s="21"/>
       <c r="CO2" s="21"/>
@@ -1409,13 +1423,27 @@
       <c r="CI4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="CK4" s="19"/>
-      <c r="CL4" s="19"/>
-      <c r="CM4" s="18"/>
-      <c r="CN4" s="17"/>
-      <c r="CO4" s="16"/>
-      <c r="CP4" s="16"/>
-      <c r="CQ4" s="16"/>
+      <c r="CK4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="CL4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="CM4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="CN4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="CO4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="CP4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="CQ4" s="16" t="s">
+        <v>14</v>
+      </c>
       <c r="CS4" s="19"/>
       <c r="CT4" s="19"/>
       <c r="CU4" s="18"/>
@@ -1669,13 +1697,28 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CJ5" s="38"/>
-      <c r="CK5" s="14"/>
-      <c r="CL5" s="32"/>
-      <c r="CM5" s="15"/>
+      <c r="CK5" s="14">
+        <v>75</v>
+      </c>
+      <c r="CL5" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CM5" s="15">
+        <v>6082</v>
+      </c>
       <c r="CN5" s="33"/>
-      <c r="CO5" s="10"/>
-      <c r="CP5" s="12"/>
-      <c r="CQ5" s="11"/>
+      <c r="CO5" s="10">
+        <f t="shared" ref="CO5:CO65" si="26">CM5-CE5</f>
+        <v>-404</v>
+      </c>
+      <c r="CP5" s="12">
+        <f t="shared" ref="CP5:CP65" si="27">CN5-CF5</f>
+        <v>0</v>
+      </c>
+      <c r="CQ5" s="11" t="e">
+        <f t="shared" ref="CQ5:CQ65" si="28">(CN5-CF5)/CF5</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CR5" s="38"/>
       <c r="CS5" s="14"/>
       <c r="CT5" s="32"/>
@@ -1897,11 +1940,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK6" s="14"/>
-      <c r="CL6" s="32"/>
+      <c r="CL6" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CN6" s="33"/>
-      <c r="CO6" s="10"/>
-      <c r="CP6" s="12"/>
-      <c r="CQ6" s="11"/>
+      <c r="CO6" s="10">
+        <f t="shared" si="26"/>
+        <v>-15</v>
+      </c>
+      <c r="CP6" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ6" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS6" s="14"/>
       <c r="CT6" s="32"/>
       <c r="CV6" s="33"/>
@@ -2143,10 +2197,27 @@
         <v>-3.9739672708067282E-2</v>
       </c>
       <c r="CK7" s="14"/>
-      <c r="CL7" s="13"/>
-      <c r="CN7" s="12"/>
-      <c r="CP7" s="12"/>
-      <c r="CQ7" s="11"/>
+      <c r="CL7" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CM7" s="10">
+        <v>171</v>
+      </c>
+      <c r="CN7" s="12">
+        <v>178639.99999928992</v>
+      </c>
+      <c r="CO7" s="10">
+        <f t="shared" si="26"/>
+        <v>-15</v>
+      </c>
+      <c r="CP7" s="12">
+        <f t="shared" si="27"/>
+        <v>-39869.523809400009</v>
+      </c>
+      <c r="CQ7" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.18246126353882261</v>
+      </c>
       <c r="CS7" s="14"/>
       <c r="CT7" s="13"/>
       <c r="CV7" s="12"/>
@@ -2387,10 +2458,27 @@
         <v>-9.1248074625875322E-2</v>
       </c>
       <c r="CK8" s="14"/>
-      <c r="CL8" s="13"/>
-      <c r="CN8" s="12"/>
-      <c r="CP8" s="12"/>
-      <c r="CQ8" s="11"/>
+      <c r="CL8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CM8" s="10">
+        <v>217</v>
+      </c>
+      <c r="CN8" s="12">
+        <v>242963.80952367</v>
+      </c>
+      <c r="CO8" s="10">
+        <f t="shared" si="26"/>
+        <v>-16</v>
+      </c>
+      <c r="CP8" s="12">
+        <f t="shared" si="27"/>
+        <v>-37419.047619019926</v>
+      </c>
+      <c r="CQ8" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.13345697379771318</v>
+      </c>
       <c r="CS8" s="14"/>
       <c r="CT8" s="13"/>
       <c r="CV8" s="12"/>
@@ -2631,10 +2719,27 @@
         <v>2.0457961621817462E-2</v>
       </c>
       <c r="CK9" s="14"/>
-      <c r="CL9" s="13"/>
-      <c r="CN9" s="12"/>
-      <c r="CP9" s="12"/>
-      <c r="CQ9" s="11"/>
+      <c r="CL9" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM9" s="10">
+        <v>70</v>
+      </c>
+      <c r="CN9" s="12">
+        <v>455047.61904759996</v>
+      </c>
+      <c r="CO9" s="10">
+        <f t="shared" si="26"/>
+        <v>-5</v>
+      </c>
+      <c r="CP9" s="12">
+        <f t="shared" si="27"/>
+        <v>-42809.523809530016</v>
+      </c>
+      <c r="CQ9" s="11">
+        <f t="shared" si="28"/>
+        <v>-8.5987565758025214E-2</v>
+      </c>
       <c r="CS9" s="14"/>
       <c r="CT9" s="13"/>
       <c r="CV9" s="12"/>
@@ -2875,10 +2980,27 @@
         <v>0.13501760198801455</v>
       </c>
       <c r="CK10" s="14"/>
-      <c r="CL10" s="13"/>
-      <c r="CN10" s="12"/>
-      <c r="CP10" s="12"/>
-      <c r="CQ10" s="11"/>
+      <c r="CL10" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CM10" s="10">
+        <v>35</v>
+      </c>
+      <c r="CN10" s="12">
+        <v>483333.33333326003</v>
+      </c>
+      <c r="CO10" s="10">
+        <f t="shared" si="26"/>
+        <v>-4</v>
+      </c>
+      <c r="CP10" s="12">
+        <f t="shared" si="27"/>
+        <v>-38666.666666670004</v>
+      </c>
+      <c r="CQ10" s="11">
+        <f t="shared" si="28"/>
+        <v>-7.407407407409039E-2</v>
+      </c>
       <c r="CS10" s="14"/>
       <c r="CT10" s="13"/>
       <c r="CV10" s="12"/>
@@ -3094,10 +3216,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK11" s="14"/>
-      <c r="CL11" s="13"/>
+      <c r="CL11" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="CN11" s="12"/>
-      <c r="CP11" s="12"/>
-      <c r="CQ11" s="11"/>
+      <c r="CO11" s="10">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="CP11" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ11" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS11" s="14"/>
       <c r="CT11" s="13"/>
       <c r="CV11" s="12"/>
@@ -3338,10 +3472,27 @@
         <v>-5.84315735520246E-2</v>
       </c>
       <c r="CK12" s="14"/>
-      <c r="CL12" s="13"/>
-      <c r="CN12" s="12"/>
-      <c r="CP12" s="12"/>
-      <c r="CQ12" s="11"/>
+      <c r="CL12" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CM12" s="10">
+        <v>11</v>
+      </c>
+      <c r="CN12" s="12">
+        <v>64090</v>
+      </c>
+      <c r="CO12" s="10">
+        <f t="shared" si="26"/>
+        <v>5</v>
+      </c>
+      <c r="CP12" s="12">
+        <f t="shared" si="27"/>
+        <v>27350</v>
+      </c>
+      <c r="CQ12" s="11">
+        <f t="shared" si="28"/>
+        <v>0.74442025040827431</v>
+      </c>
       <c r="CS12" s="14"/>
       <c r="CT12" s="13"/>
       <c r="CV12" s="12"/>
@@ -3582,10 +3733,27 @@
         <v>0.16751719189620934</v>
       </c>
       <c r="CK13" s="14"/>
-      <c r="CL13" s="13"/>
-      <c r="CN13" s="12"/>
-      <c r="CP13" s="12"/>
-      <c r="CQ13" s="11"/>
+      <c r="CL13" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CM13" s="10">
+        <v>8</v>
+      </c>
+      <c r="CN13" s="12">
+        <v>341723.80952377006</v>
+      </c>
+      <c r="CO13" s="10">
+        <f t="shared" si="26"/>
+        <v>-10</v>
+      </c>
+      <c r="CP13" s="12">
+        <f t="shared" si="27"/>
+        <v>-347895.23809520988</v>
+      </c>
+      <c r="CQ13" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.50447452009391824</v>
+      </c>
       <c r="CS13" s="14"/>
       <c r="CT13" s="13"/>
       <c r="CV13" s="12"/>
@@ -3826,10 +3994,27 @@
         <v>-3.1286756057433383E-2</v>
       </c>
       <c r="CK14" s="14"/>
-      <c r="CL14" s="13"/>
-      <c r="CN14" s="12"/>
-      <c r="CP14" s="12"/>
-      <c r="CQ14" s="11"/>
+      <c r="CL14" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CM14" s="10">
+        <v>24</v>
+      </c>
+      <c r="CN14" s="12">
+        <v>438571.42857138999</v>
+      </c>
+      <c r="CO14" s="10">
+        <f t="shared" si="26"/>
+        <v>-19</v>
+      </c>
+      <c r="CP14" s="12">
+        <f t="shared" si="27"/>
+        <v>-345809.52380948002</v>
+      </c>
+      <c r="CQ14" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.44086935405535715</v>
+      </c>
       <c r="CS14" s="14"/>
       <c r="CT14" s="13"/>
       <c r="CV14" s="12"/>
@@ -4070,10 +4255,27 @@
         <v>1.5411748666271627</v>
       </c>
       <c r="CK15" s="14"/>
-      <c r="CL15" s="13"/>
-      <c r="CN15" s="12"/>
-      <c r="CP15" s="12"/>
-      <c r="CQ15" s="11"/>
+      <c r="CL15" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CM15" s="10">
+        <v>115</v>
+      </c>
+      <c r="CN15" s="12">
+        <v>4159523.8095237301</v>
+      </c>
+      <c r="CO15" s="10">
+        <f t="shared" si="26"/>
+        <v>-44</v>
+      </c>
+      <c r="CP15" s="12">
+        <f t="shared" si="27"/>
+        <v>-1964707.6190476301</v>
+      </c>
+      <c r="CQ15" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.32080884629566497</v>
+      </c>
       <c r="CS15" s="14"/>
       <c r="CT15" s="13"/>
       <c r="CV15" s="12"/>
@@ -4314,13 +4516,28 @@
         <f t="shared" si="25"/>
         <v>0.71634137443294743</v>
       </c>
-      <c r="CK16" s="9"/>
+      <c r="CK16" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="CL16" s="9"/>
-      <c r="CM16" s="8"/>
-      <c r="CN16" s="7"/>
-      <c r="CO16" s="27"/>
-      <c r="CP16" s="28"/>
-      <c r="CQ16" s="29"/>
+      <c r="CM16" s="8">
+        <v>651</v>
+      </c>
+      <c r="CN16" s="7">
+        <v>6363893.8095227107</v>
+      </c>
+      <c r="CO16" s="27">
+        <f t="shared" si="26"/>
+        <v>-108</v>
+      </c>
+      <c r="CP16" s="28">
+        <f t="shared" si="27"/>
+        <v>-2789827.1428569388</v>
+      </c>
+      <c r="CQ16" s="29">
+        <f t="shared" si="28"/>
+        <v>-0.30477520096695548</v>
+      </c>
       <c r="CS16" s="9"/>
       <c r="CT16" s="9"/>
       <c r="CU16" s="8"/>
@@ -4562,13 +4779,28 @@
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CK17" s="14"/>
-      <c r="CL17" s="32"/>
-      <c r="CM17" s="15"/>
+      <c r="CK17" s="14">
+        <v>76</v>
+      </c>
+      <c r="CL17" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CM17" s="15">
+        <v>5349</v>
+      </c>
       <c r="CN17" s="33"/>
-      <c r="CO17" s="10"/>
-      <c r="CP17" s="12"/>
-      <c r="CQ17" s="11"/>
+      <c r="CO17" s="10">
+        <f t="shared" si="26"/>
+        <v>-193</v>
+      </c>
+      <c r="CP17" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ17" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS17" s="14"/>
       <c r="CT17" s="32"/>
       <c r="CU17" s="15"/>
@@ -4789,12 +5021,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK18" s="14"/>
-      <c r="CL18" s="32"/>
+      <c r="CL18" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CM18" s="15"/>
       <c r="CN18" s="33"/>
-      <c r="CO18" s="10"/>
-      <c r="CP18" s="12"/>
-      <c r="CQ18" s="11"/>
+      <c r="CO18" s="10">
+        <f t="shared" si="26"/>
+        <v>-13</v>
+      </c>
+      <c r="CP18" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ18" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS18" s="14"/>
       <c r="CT18" s="32"/>
       <c r="CU18" s="15"/>
@@ -5037,10 +5280,27 @@
         <v>0.83226108505740837</v>
       </c>
       <c r="CK19" s="14"/>
-      <c r="CL19" s="13"/>
-      <c r="CN19" s="12"/>
-      <c r="CP19" s="12"/>
-      <c r="CQ19" s="11"/>
+      <c r="CL19" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CM19" s="10">
+        <v>211</v>
+      </c>
+      <c r="CN19" s="12">
+        <v>232219.04761820004</v>
+      </c>
+      <c r="CO19" s="10">
+        <f t="shared" si="26"/>
+        <v>7</v>
+      </c>
+      <c r="CP19" s="12">
+        <f t="shared" si="27"/>
+        <v>16041.904761850077</v>
+      </c>
+      <c r="CQ19" s="11">
+        <f t="shared" si="28"/>
+        <v>7.4207219828554896E-2</v>
+      </c>
       <c r="CS19" s="14"/>
       <c r="CT19" s="13"/>
       <c r="CV19" s="12"/>
@@ -5281,10 +5541,27 @@
         <v>0.48836853949280895</v>
       </c>
       <c r="CK20" s="14"/>
-      <c r="CL20" s="13"/>
-      <c r="CN20" s="12"/>
-      <c r="CP20" s="12"/>
-      <c r="CQ20" s="11"/>
+      <c r="CL20" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CM20" s="10">
+        <v>219</v>
+      </c>
+      <c r="CN20" s="12">
+        <v>218466.66666655001</v>
+      </c>
+      <c r="CO20" s="10">
+        <f t="shared" si="26"/>
+        <v>-34</v>
+      </c>
+      <c r="CP20" s="12">
+        <f t="shared" si="27"/>
+        <v>-87663.809523779986</v>
+      </c>
+      <c r="CQ20" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.28636093542440028</v>
+      </c>
       <c r="CS20" s="14"/>
       <c r="CT20" s="13"/>
       <c r="CV20" s="12"/>
@@ -5525,10 +5802,27 @@
         <v>-0.25263614666959294</v>
       </c>
       <c r="CK21" s="14"/>
-      <c r="CL21" s="13"/>
-      <c r="CN21" s="12"/>
-      <c r="CP21" s="12"/>
-      <c r="CQ21" s="11"/>
+      <c r="CL21" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM21" s="10">
+        <v>61</v>
+      </c>
+      <c r="CN21" s="12">
+        <v>369134.28571425995</v>
+      </c>
+      <c r="CO21" s="10">
+        <f t="shared" si="26"/>
+        <v>7</v>
+      </c>
+      <c r="CP21" s="12">
+        <f t="shared" si="27"/>
+        <v>41077.14285713993</v>
+      </c>
+      <c r="CQ21" s="11">
+        <f t="shared" si="28"/>
+        <v>0.12521337746037256</v>
+      </c>
       <c r="CS21" s="14"/>
       <c r="CT21" s="13"/>
       <c r="CV21" s="12"/>
@@ -5769,10 +6063,27 @@
         <v>0.11880096980384325</v>
       </c>
       <c r="CK22" s="14"/>
-      <c r="CL22" s="13"/>
-      <c r="CN22" s="12"/>
-      <c r="CP22" s="12"/>
-      <c r="CQ22" s="11"/>
+      <c r="CL22" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CM22" s="10">
+        <v>48</v>
+      </c>
+      <c r="CN22" s="12">
+        <v>595904.76190469007</v>
+      </c>
+      <c r="CO22" s="10">
+        <f t="shared" si="26"/>
+        <v>9</v>
+      </c>
+      <c r="CP22" s="12">
+        <f t="shared" si="27"/>
+        <v>112476.19047618011</v>
+      </c>
+      <c r="CQ22" s="11">
+        <f t="shared" si="28"/>
+        <v>0.23266351457841633</v>
+      </c>
       <c r="CS22" s="14"/>
       <c r="CT22" s="13"/>
       <c r="CV22" s="12"/>
@@ -6003,10 +6314,27 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK23" s="14"/>
-      <c r="CL23" s="13"/>
-      <c r="CN23" s="12"/>
-      <c r="CP23" s="12"/>
-      <c r="CQ23" s="11"/>
+      <c r="CL23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="CM23" s="10">
+        <v>16</v>
+      </c>
+      <c r="CN23" s="12">
+        <v>90340</v>
+      </c>
+      <c r="CO23" s="10">
+        <f t="shared" si="26"/>
+        <v>14</v>
+      </c>
+      <c r="CP23" s="12">
+        <f t="shared" si="27"/>
+        <v>78825.714285719994</v>
+      </c>
+      <c r="CQ23" s="11">
+        <f t="shared" si="28"/>
+        <v>6.8459057071999236</v>
+      </c>
       <c r="CS23" s="14"/>
       <c r="CT23" s="13"/>
       <c r="CV23" s="12"/>
@@ -6247,10 +6575,22 @@
         <v>1.2908811924594477</v>
       </c>
       <c r="CK24" s="14"/>
-      <c r="CL24" s="13"/>
+      <c r="CL24" s="13" t="s">
+        <v>5</v>
+      </c>
       <c r="CN24" s="12"/>
-      <c r="CP24" s="12"/>
-      <c r="CQ24" s="11"/>
+      <c r="CO24" s="10">
+        <f t="shared" si="26"/>
+        <v>-19</v>
+      </c>
+      <c r="CP24" s="12">
+        <f t="shared" si="27"/>
+        <v>-104510</v>
+      </c>
+      <c r="CQ24" s="11">
+        <f t="shared" si="28"/>
+        <v>-1</v>
+      </c>
       <c r="CS24" s="14"/>
       <c r="CT24" s="13"/>
       <c r="CV24" s="12"/>
@@ -6491,10 +6831,27 @@
         <v>0.83569942797729235</v>
       </c>
       <c r="CK25" s="14"/>
-      <c r="CL25" s="13"/>
-      <c r="CN25" s="12"/>
-      <c r="CP25" s="12"/>
-      <c r="CQ25" s="11"/>
+      <c r="CL25" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CM25" s="10">
+        <v>5</v>
+      </c>
+      <c r="CN25" s="12">
+        <v>139528.57142856001</v>
+      </c>
+      <c r="CO25" s="10">
+        <f t="shared" si="26"/>
+        <v>-4</v>
+      </c>
+      <c r="CP25" s="12">
+        <f t="shared" si="27"/>
+        <v>-196666.66666665999</v>
+      </c>
+      <c r="CQ25" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.5849775498930726</v>
+      </c>
       <c r="CS25" s="14"/>
       <c r="CT25" s="13"/>
       <c r="CV25" s="12"/>
@@ -6735,10 +7092,27 @@
         <v>0.58923788653517695</v>
       </c>
       <c r="CK26" s="14"/>
-      <c r="CL26" s="13"/>
-      <c r="CN26" s="12"/>
-      <c r="CP26" s="12"/>
-      <c r="CQ26" s="11"/>
+      <c r="CL26" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CM26" s="10">
+        <v>39</v>
+      </c>
+      <c r="CN26" s="12">
+        <v>642761.90476185002</v>
+      </c>
+      <c r="CO26" s="10">
+        <f t="shared" si="26"/>
+        <v>5</v>
+      </c>
+      <c r="CP26" s="12">
+        <f t="shared" si="27"/>
+        <v>21142.857142879977</v>
+      </c>
+      <c r="CQ26" s="11">
+        <f t="shared" si="28"/>
+        <v>3.4012563199060437E-2</v>
+      </c>
       <c r="CS26" s="14"/>
       <c r="CT26" s="13"/>
       <c r="CV26" s="12"/>
@@ -6979,10 +7353,27 @@
         <v>6.7272727272728154</v>
       </c>
       <c r="CK27" s="14"/>
-      <c r="CL27" s="13"/>
-      <c r="CN27" s="12"/>
-      <c r="CP27" s="12"/>
-      <c r="CQ27" s="11"/>
+      <c r="CL27" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CM27" s="10">
+        <v>188</v>
+      </c>
+      <c r="CN27" s="12">
+        <v>6769714.2857141895</v>
+      </c>
+      <c r="CO27" s="10">
+        <f t="shared" si="26"/>
+        <v>43</v>
+      </c>
+      <c r="CP27" s="12">
+        <f t="shared" si="27"/>
+        <v>1661619.0476190401</v>
+      </c>
+      <c r="CQ27" s="11">
+        <f t="shared" si="28"/>
+        <v>0.32529132096579144</v>
+      </c>
       <c r="CS27" s="14"/>
       <c r="CT27" s="13"/>
       <c r="CV27" s="12"/>
@@ -7223,13 +7614,28 @@
         <f t="shared" si="25"/>
         <v>2.0358396968594983</v>
       </c>
-      <c r="CK28" s="9"/>
+      <c r="CK28" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="CL28" s="9"/>
-      <c r="CM28" s="8"/>
-      <c r="CN28" s="7"/>
-      <c r="CO28" s="27"/>
-      <c r="CP28" s="28"/>
-      <c r="CQ28" s="29"/>
+      <c r="CM28" s="8">
+        <v>787</v>
+      </c>
+      <c r="CN28" s="7">
+        <v>9058069.5238083005</v>
+      </c>
+      <c r="CO28" s="27">
+        <f t="shared" si="26"/>
+        <v>28</v>
+      </c>
+      <c r="CP28" s="28">
+        <f t="shared" si="27"/>
+        <v>1542342.3809523713</v>
+      </c>
+      <c r="CQ28" s="29">
+        <f t="shared" si="28"/>
+        <v>0.20521532403134726</v>
+      </c>
       <c r="CS28" s="9"/>
       <c r="CT28" s="9"/>
       <c r="CU28" s="8"/>
@@ -7471,13 +7877,28 @@
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CK29" s="14"/>
-      <c r="CL29" s="32"/>
-      <c r="CM29" s="15"/>
+      <c r="CK29" s="14">
+        <v>77</v>
+      </c>
+      <c r="CL29" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CM29" s="15">
+        <v>3439</v>
+      </c>
       <c r="CN29" s="33"/>
-      <c r="CO29" s="10"/>
-      <c r="CP29" s="12"/>
-      <c r="CQ29" s="11"/>
+      <c r="CO29" s="10">
+        <f t="shared" si="26"/>
+        <v>-63</v>
+      </c>
+      <c r="CP29" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ29" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS29" s="14"/>
       <c r="CT29" s="32"/>
       <c r="CU29" s="15"/>
@@ -7698,12 +8119,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK30" s="14"/>
-      <c r="CL30" s="32"/>
+      <c r="CL30" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CM30" s="15"/>
       <c r="CN30" s="33"/>
-      <c r="CO30" s="10"/>
-      <c r="CP30" s="12"/>
-      <c r="CQ30" s="11"/>
+      <c r="CO30" s="10">
+        <f t="shared" si="26"/>
+        <v>-3</v>
+      </c>
+      <c r="CP30" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ30" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS30" s="14"/>
       <c r="CT30" s="32"/>
       <c r="CU30" s="15"/>
@@ -7946,10 +8378,27 @@
         <v>-0.25559529515919094</v>
       </c>
       <c r="CK31" s="14"/>
-      <c r="CL31" s="13"/>
-      <c r="CN31" s="12"/>
-      <c r="CP31" s="12"/>
-      <c r="CQ31" s="11"/>
+      <c r="CL31" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CM31" s="10">
+        <v>71</v>
+      </c>
+      <c r="CN31" s="12">
+        <v>66044.761904450017</v>
+      </c>
+      <c r="CO31" s="10">
+        <f t="shared" si="26"/>
+        <v>-16</v>
+      </c>
+      <c r="CP31" s="12">
+        <f t="shared" si="27"/>
+        <v>-10865.714285640017</v>
+      </c>
+      <c r="CQ31" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.14127742830228468</v>
+      </c>
       <c r="CS31" s="14"/>
       <c r="CT31" s="13"/>
       <c r="CV31" s="12"/>
@@ -8190,10 +8639,27 @@
         <v>2.382807130273138E-3</v>
       </c>
       <c r="CK32" s="14"/>
-      <c r="CL32" s="13"/>
-      <c r="CN32" s="12"/>
-      <c r="CP32" s="12"/>
-      <c r="CQ32" s="11"/>
+      <c r="CL32" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CM32" s="10">
+        <v>77</v>
+      </c>
+      <c r="CN32" s="12">
+        <v>78773.333333229995</v>
+      </c>
+      <c r="CO32" s="10">
+        <f t="shared" si="26"/>
+        <v>-3</v>
+      </c>
+      <c r="CP32" s="12">
+        <f t="shared" si="27"/>
+        <v>-4560</v>
+      </c>
+      <c r="CQ32" s="11">
+        <f t="shared" si="28"/>
+        <v>-5.4720000000067853E-2</v>
+      </c>
       <c r="CS32" s="14"/>
       <c r="CT32" s="13"/>
       <c r="CV32" s="12"/>
@@ -8434,10 +8900,27 @@
         <v>-0.46149294492488274</v>
       </c>
       <c r="CK33" s="14"/>
-      <c r="CL33" s="13"/>
-      <c r="CN33" s="12"/>
-      <c r="CP33" s="12"/>
-      <c r="CQ33" s="11"/>
+      <c r="CL33" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM33" s="10">
+        <v>25</v>
+      </c>
+      <c r="CN33" s="12">
+        <v>172619.04761904001</v>
+      </c>
+      <c r="CO33" s="10">
+        <f t="shared" si="26"/>
+        <v>6</v>
+      </c>
+      <c r="CP33" s="12">
+        <f t="shared" si="27"/>
+        <v>59942.857142860012</v>
+      </c>
+      <c r="CQ33" s="11">
+        <f t="shared" si="28"/>
+        <v>0.53199222381885614</v>
+      </c>
       <c r="CS33" s="14"/>
       <c r="CT33" s="13"/>
       <c r="CV33" s="12"/>
@@ -8678,10 +9161,27 @@
         <v>-0.54887820512820562</v>
       </c>
       <c r="CK34" s="14"/>
-      <c r="CL34" s="13"/>
-      <c r="CN34" s="12"/>
-      <c r="CP34" s="12"/>
-      <c r="CQ34" s="11"/>
+      <c r="CL34" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CM34" s="10">
+        <v>10</v>
+      </c>
+      <c r="CN34" s="12">
+        <v>127142.85714282002</v>
+      </c>
+      <c r="CO34" s="10">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="CP34" s="12">
+        <f t="shared" si="27"/>
+        <v>19904.761904750019</v>
+      </c>
+      <c r="CQ34" s="11">
+        <f t="shared" si="28"/>
+        <v>0.18561278863225966</v>
+      </c>
       <c r="CS34" s="14"/>
       <c r="CT34" s="13"/>
       <c r="CV34" s="12"/>
@@ -8902,10 +9402,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK35" s="14"/>
-      <c r="CL35" s="13"/>
+      <c r="CL35" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="CN35" s="12"/>
-      <c r="CP35" s="12"/>
-      <c r="CQ35" s="11"/>
+      <c r="CO35" s="10">
+        <f t="shared" si="26"/>
+        <v>-1</v>
+      </c>
+      <c r="CP35" s="12">
+        <f t="shared" si="27"/>
+        <v>-8857.1428571399993</v>
+      </c>
+      <c r="CQ35" s="11">
+        <f t="shared" si="28"/>
+        <v>-1</v>
+      </c>
       <c r="CS35" s="14"/>
       <c r="CT35" s="13"/>
       <c r="CV35" s="12"/>
@@ -9136,10 +9648,27 @@
         <v>7.8098471993261484E-3</v>
       </c>
       <c r="CK36" s="14"/>
-      <c r="CL36" s="13"/>
-      <c r="CN36" s="12"/>
-      <c r="CP36" s="12"/>
-      <c r="CQ36" s="11"/>
+      <c r="CL36" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CM36" s="10">
+        <v>2</v>
+      </c>
+      <c r="CN36" s="12">
+        <v>8180</v>
+      </c>
+      <c r="CO36" s="10">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="CP36" s="12">
+        <f t="shared" si="27"/>
+        <v>-300</v>
+      </c>
+      <c r="CQ36" s="11">
+        <f t="shared" si="28"/>
+        <v>-3.5377358490566037E-2</v>
+      </c>
       <c r="CS36" s="14"/>
       <c r="CT36" s="13"/>
       <c r="CV36" s="12"/>
@@ -9341,7 +9870,7 @@
         <v>26147.619047609998</v>
       </c>
       <c r="BY37" s="10">
-        <f t="shared" ref="BY37:BY65" si="26">BW37-BO37</f>
+        <f t="shared" ref="BY37:BY65" si="29">BW37-BO37</f>
         <v>1</v>
       </c>
       <c r="BZ37" s="12">
@@ -9375,10 +9904,27 @@
         <v>2.2299034784197485</v>
       </c>
       <c r="CK37" s="14"/>
-      <c r="CL37" s="13"/>
-      <c r="CN37" s="12"/>
-      <c r="CP37" s="12"/>
-      <c r="CQ37" s="11"/>
+      <c r="CL37" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CM37" s="10">
+        <v>1</v>
+      </c>
+      <c r="CN37" s="12">
+        <v>47047.619047610002</v>
+      </c>
+      <c r="CO37" s="10">
+        <f t="shared" si="26"/>
+        <v>-2</v>
+      </c>
+      <c r="CP37" s="12">
+        <f t="shared" si="27"/>
+        <v>-37406.666666660007</v>
+      </c>
+      <c r="CQ37" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.44292206547357615</v>
+      </c>
       <c r="CS37" s="14"/>
       <c r="CT37" s="13"/>
       <c r="CV37" s="12"/>
@@ -9585,7 +10131,7 @@
         <v>154190.47619044999</v>
       </c>
       <c r="BY38" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-1</v>
       </c>
       <c r="BZ38" s="12">
@@ -9619,10 +10165,27 @@
         <v>0.16924027177267556</v>
       </c>
       <c r="CK38" s="14"/>
-      <c r="CL38" s="13"/>
-      <c r="CN38" s="12"/>
-      <c r="CP38" s="12"/>
-      <c r="CQ38" s="11"/>
+      <c r="CL38" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CM38" s="10">
+        <v>14</v>
+      </c>
+      <c r="CN38" s="12">
+        <v>246190.47619043995</v>
+      </c>
+      <c r="CO38" s="10">
+        <f t="shared" si="26"/>
+        <v>3</v>
+      </c>
+      <c r="CP38" s="12">
+        <f t="shared" si="27"/>
+        <v>65904.761904759944</v>
+      </c>
+      <c r="CQ38" s="11">
+        <f t="shared" si="28"/>
+        <v>0.36555731642900741</v>
+      </c>
       <c r="CS38" s="14"/>
       <c r="CT38" s="13"/>
       <c r="CV38" s="12"/>
@@ -9829,7 +10392,7 @@
         <v>379739.04761903</v>
       </c>
       <c r="BY39" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4</v>
       </c>
       <c r="BZ39" s="12">
@@ -9863,10 +10426,27 @@
         <v>0.19756424211114065</v>
       </c>
       <c r="CK39" s="14"/>
-      <c r="CL39" s="13"/>
-      <c r="CN39" s="12"/>
-      <c r="CP39" s="12"/>
-      <c r="CQ39" s="11"/>
+      <c r="CL39" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CM39" s="10">
+        <v>13</v>
+      </c>
+      <c r="CN39" s="12">
+        <v>457809.52380949992</v>
+      </c>
+      <c r="CO39" s="10">
+        <f t="shared" si="26"/>
+        <v>-2</v>
+      </c>
+      <c r="CP39" s="12">
+        <f t="shared" si="27"/>
+        <v>3047.6190476099146</v>
+      </c>
+      <c r="CQ39" s="11">
+        <f t="shared" si="28"/>
+        <v>6.7015706806084069E-3</v>
+      </c>
       <c r="CS39" s="14"/>
       <c r="CT39" s="13"/>
       <c r="CV39" s="12"/>
@@ -10074,7 +10654,7 @@
         <v>1201897.14285643</v>
       </c>
       <c r="BY40" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-1</v>
       </c>
       <c r="BZ40" s="28">
@@ -10107,13 +10687,28 @@
         <f t="shared" si="25"/>
         <v>-7.0638324173154007E-2</v>
       </c>
-      <c r="CK40" s="9"/>
+      <c r="CK40" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="CL40" s="9"/>
-      <c r="CM40" s="8"/>
-      <c r="CN40" s="7"/>
-      <c r="CO40" s="27"/>
-      <c r="CP40" s="28"/>
-      <c r="CQ40" s="29"/>
+      <c r="CM40" s="8">
+        <v>213</v>
+      </c>
+      <c r="CN40" s="7">
+        <v>1203807.6190470899</v>
+      </c>
+      <c r="CO40" s="27">
+        <f t="shared" si="26"/>
+        <v>-14</v>
+      </c>
+      <c r="CP40" s="28">
+        <f t="shared" si="27"/>
+        <v>86810.476190540008</v>
+      </c>
+      <c r="CQ40" s="29">
+        <f t="shared" si="28"/>
+        <v>7.7717724477374628E-2</v>
+      </c>
       <c r="CS40" s="9"/>
       <c r="CT40" s="9"/>
       <c r="CU40" s="8"/>
@@ -10322,7 +10917,7 @@
       </c>
       <c r="BX41" s="33"/>
       <c r="BY41" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-543</v>
       </c>
       <c r="BZ41" s="12">
@@ -10355,13 +10950,28 @@
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CK41" s="14"/>
-      <c r="CL41" s="32"/>
-      <c r="CM41" s="15"/>
+      <c r="CK41" s="14">
+        <v>81</v>
+      </c>
+      <c r="CL41" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CM41" s="15">
+        <v>1323</v>
+      </c>
       <c r="CN41" s="33"/>
-      <c r="CO41" s="10"/>
-      <c r="CP41" s="12"/>
-      <c r="CQ41" s="11"/>
+      <c r="CO41" s="10">
+        <f t="shared" si="26"/>
+        <v>38</v>
+      </c>
+      <c r="CP41" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ41" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS41" s="14"/>
       <c r="CT41" s="32"/>
       <c r="CU41" s="15"/>
@@ -10550,7 +11160,7 @@
       </c>
       <c r="BX42" s="33"/>
       <c r="BY42" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-4</v>
       </c>
       <c r="BZ42" s="12">
@@ -10582,12 +11192,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK42" s="14"/>
-      <c r="CL42" s="32"/>
+      <c r="CL42" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CM42" s="15"/>
       <c r="CN42" s="33"/>
-      <c r="CO42" s="10"/>
-      <c r="CP42" s="12"/>
-      <c r="CQ42" s="11"/>
+      <c r="CO42" s="10">
+        <f t="shared" si="26"/>
+        <v>-7</v>
+      </c>
+      <c r="CP42" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ42" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS42" s="14"/>
       <c r="CT42" s="32"/>
       <c r="CU42" s="15"/>
@@ -10796,7 +11417,7 @@
         <v>82412.380952079999</v>
       </c>
       <c r="BY43" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-55</v>
       </c>
       <c r="BZ43" s="12">
@@ -10830,10 +11451,27 @@
         <v>3.8101071265928071E-2</v>
       </c>
       <c r="CK43" s="14"/>
-      <c r="CL43" s="13"/>
-      <c r="CN43" s="12"/>
-      <c r="CP43" s="12"/>
-      <c r="CQ43" s="11"/>
+      <c r="CL43" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CM43" s="10">
+        <v>98</v>
+      </c>
+      <c r="CN43" s="12">
+        <v>89394.285713870035</v>
+      </c>
+      <c r="CO43" s="10">
+        <f t="shared" si="26"/>
+        <v>-12</v>
+      </c>
+      <c r="CP43" s="12">
+        <f t="shared" si="27"/>
+        <v>3841.9047619400226</v>
+      </c>
+      <c r="CQ43" s="11">
+        <f t="shared" si="28"/>
+        <v>4.4907046644309105E-2</v>
+      </c>
       <c r="CS43" s="14"/>
       <c r="CT43" s="13"/>
       <c r="CV43" s="12"/>
@@ -11040,7 +11678,7 @@
         <v>90152.380952249994</v>
       </c>
       <c r="BY44" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>3</v>
       </c>
       <c r="BZ44" s="12">
@@ -11074,10 +11712,27 @@
         <v>-1.4874286921387718E-2</v>
       </c>
       <c r="CK44" s="14"/>
-      <c r="CL44" s="13"/>
-      <c r="CN44" s="12"/>
-      <c r="CP44" s="12"/>
-      <c r="CQ44" s="11"/>
+      <c r="CL44" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CM44" s="10">
+        <v>75</v>
+      </c>
+      <c r="CN44" s="12">
+        <v>66047.619047519998</v>
+      </c>
+      <c r="CO44" s="10">
+        <f t="shared" si="26"/>
+        <v>-13</v>
+      </c>
+      <c r="CP44" s="12">
+        <f t="shared" si="27"/>
+        <v>-22763.809523799981</v>
+      </c>
+      <c r="CQ44" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.25631621841911384</v>
+      </c>
       <c r="CS44" s="14"/>
       <c r="CT44" s="13"/>
       <c r="CV44" s="12"/>
@@ -11284,7 +11939,7 @@
         <v>92723.80952380001</v>
       </c>
       <c r="BY45" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-2</v>
       </c>
       <c r="BZ45" s="12">
@@ -11318,10 +11973,27 @@
         <v>0.50386195562864633</v>
       </c>
       <c r="CK45" s="14"/>
-      <c r="CL45" s="13"/>
-      <c r="CN45" s="12"/>
-      <c r="CP45" s="12"/>
-      <c r="CQ45" s="11"/>
+      <c r="CL45" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM45" s="10">
+        <v>10</v>
+      </c>
+      <c r="CN45" s="12">
+        <v>62761.904761899998</v>
+      </c>
+      <c r="CO45" s="10">
+        <f t="shared" si="26"/>
+        <v>-11</v>
+      </c>
+      <c r="CP45" s="12">
+        <f t="shared" si="27"/>
+        <v>-76681.90476189999</v>
+      </c>
+      <c r="CQ45" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.54991257786034653</v>
+      </c>
       <c r="CS45" s="14"/>
       <c r="CT45" s="13"/>
       <c r="CV45" s="12"/>
@@ -11528,7 +12200,7 @@
         <v>111428.57142854</v>
       </c>
       <c r="BY46" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>2</v>
       </c>
       <c r="BZ46" s="12">
@@ -11562,10 +12234,27 @@
         <v>0.6700854700855996</v>
       </c>
       <c r="CK46" s="14"/>
-      <c r="CL46" s="13"/>
-      <c r="CN46" s="12"/>
-      <c r="CP46" s="12"/>
-      <c r="CQ46" s="11"/>
+      <c r="CL46" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CM46" s="10">
+        <v>8</v>
+      </c>
+      <c r="CN46" s="12">
+        <v>137333.33333331</v>
+      </c>
+      <c r="CO46" s="10">
+        <f t="shared" si="26"/>
+        <v>-8</v>
+      </c>
+      <c r="CP46" s="12">
+        <f t="shared" si="27"/>
+        <v>-48761.904761890037</v>
+      </c>
+      <c r="CQ46" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.26202661207776362</v>
+      </c>
       <c r="CS46" s="14"/>
       <c r="CT46" s="13"/>
       <c r="CV46" s="12"/>
@@ -11752,7 +12441,7 @@
       </c>
       <c r="BX47" s="12"/>
       <c r="BY47" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BZ47" s="12">
@@ -11781,10 +12470,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK47" s="14"/>
-      <c r="CL47" s="13"/>
+      <c r="CL47" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="CN47" s="12"/>
-      <c r="CP47" s="12"/>
-      <c r="CQ47" s="11"/>
+      <c r="CO47" s="10">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="CP47" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ47" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS47" s="14"/>
       <c r="CT47" s="13"/>
       <c r="CV47" s="12"/>
@@ -11991,7 +12692,7 @@
         <v>6290</v>
       </c>
       <c r="BY48" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-1</v>
       </c>
       <c r="BZ48" s="12">
@@ -12025,10 +12726,27 @@
         <v>1.4451510333863276</v>
       </c>
       <c r="CK48" s="14"/>
-      <c r="CL48" s="13"/>
-      <c r="CN48" s="12"/>
-      <c r="CP48" s="12"/>
-      <c r="CQ48" s="11"/>
+      <c r="CL48" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CM48" s="10">
+        <v>4</v>
+      </c>
+      <c r="CN48" s="12">
+        <v>20260</v>
+      </c>
+      <c r="CO48" s="10">
+        <f t="shared" si="26"/>
+        <v>2</v>
+      </c>
+      <c r="CP48" s="12">
+        <f t="shared" si="27"/>
+        <v>4880</v>
+      </c>
+      <c r="CQ48" s="11">
+        <f t="shared" si="28"/>
+        <v>0.31729518855656696</v>
+      </c>
       <c r="CS48" s="14"/>
       <c r="CT48" s="13"/>
       <c r="CV48" s="12"/>
@@ -12235,7 +12953,7 @@
         <v>52168.571428559997</v>
       </c>
       <c r="BY49" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-1</v>
       </c>
       <c r="BZ49" s="12">
@@ -12269,10 +12987,22 @@
         <v>3.3605345309168881</v>
       </c>
       <c r="CK49" s="14"/>
-      <c r="CL49" s="13"/>
+      <c r="CL49" s="13" t="s">
+        <v>4</v>
+      </c>
       <c r="CN49" s="12"/>
-      <c r="CP49" s="12"/>
-      <c r="CQ49" s="11"/>
+      <c r="CO49" s="10">
+        <f t="shared" si="26"/>
+        <v>-8</v>
+      </c>
+      <c r="CP49" s="12">
+        <f t="shared" si="27"/>
+        <v>-227482.85714284002</v>
+      </c>
+      <c r="CQ49" s="11">
+        <f t="shared" si="28"/>
+        <v>-1</v>
+      </c>
       <c r="CS49" s="14"/>
       <c r="CT49" s="13"/>
       <c r="CV49" s="12"/>
@@ -12479,7 +13209,7 @@
         <v>166761.90476188</v>
       </c>
       <c r="BY50" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-6</v>
       </c>
       <c r="BZ50" s="12">
@@ -12513,10 +13243,27 @@
         <v>0.26384922901197227</v>
       </c>
       <c r="CK50" s="14"/>
-      <c r="CL50" s="13"/>
-      <c r="CN50" s="12"/>
-      <c r="CP50" s="12"/>
-      <c r="CQ50" s="11"/>
+      <c r="CL50" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CM50" s="10">
+        <v>7</v>
+      </c>
+      <c r="CN50" s="12">
+        <v>91333.333333310002</v>
+      </c>
+      <c r="CO50" s="10">
+        <f t="shared" si="26"/>
+        <v>-7</v>
+      </c>
+      <c r="CP50" s="12">
+        <f t="shared" si="27"/>
+        <v>-119428.57142855998</v>
+      </c>
+      <c r="CQ50" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.56665160415729177</v>
+      </c>
       <c r="CS50" s="14"/>
       <c r="CT50" s="13"/>
       <c r="CV50" s="12"/>
@@ -12723,7 +13470,7 @@
         <v>370285.7142857</v>
       </c>
       <c r="BY51" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-12</v>
       </c>
       <c r="BZ51" s="12">
@@ -12757,10 +13504,27 @@
         <v>1.9855967078189383</v>
       </c>
       <c r="CK51" s="14"/>
-      <c r="CL51" s="13"/>
-      <c r="CN51" s="12"/>
-      <c r="CP51" s="12"/>
-      <c r="CQ51" s="11"/>
+      <c r="CL51" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CM51" s="10">
+        <v>26</v>
+      </c>
+      <c r="CN51" s="12">
+        <v>965142.85714284005</v>
+      </c>
+      <c r="CO51" s="10">
+        <f t="shared" si="26"/>
+        <v>-6</v>
+      </c>
+      <c r="CP51" s="12">
+        <f t="shared" si="27"/>
+        <v>-140380.95238092984</v>
+      </c>
+      <c r="CQ51" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.12698139214333357</v>
+      </c>
       <c r="CS51" s="14"/>
       <c r="CT51" s="13"/>
       <c r="CV51" s="12"/>
@@ -12968,7 +13732,7 @@
         <v>972223.33333280997</v>
       </c>
       <c r="BY52" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-72</v>
       </c>
       <c r="BZ52" s="28">
@@ -13001,13 +13765,28 @@
         <f t="shared" si="25"/>
         <v>1.1178790489549779</v>
       </c>
-      <c r="CK52" s="9"/>
+      <c r="CK52" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="CL52" s="9"/>
-      <c r="CM52" s="8"/>
-      <c r="CN52" s="7"/>
-      <c r="CO52" s="27"/>
-      <c r="CP52" s="28"/>
-      <c r="CQ52" s="29"/>
+      <c r="CM52" s="8">
+        <v>228</v>
+      </c>
+      <c r="CN52" s="7">
+        <v>1432273.33333275</v>
+      </c>
+      <c r="CO52" s="27">
+        <f t="shared" si="26"/>
+        <v>-63</v>
+      </c>
+      <c r="CP52" s="28">
+        <f t="shared" si="27"/>
+        <v>-626778.0952379799</v>
+      </c>
+      <c r="CQ52" s="29">
+        <f t="shared" si="28"/>
+        <v>-0.30440137946095486</v>
+      </c>
       <c r="CS52" s="9"/>
       <c r="CT52" s="9"/>
       <c r="CU52" s="8"/>
@@ -13188,7 +13967,7 @@
       <c r="BW53" s="15"/>
       <c r="BX53" s="33"/>
       <c r="BY53" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BZ53" s="12">
@@ -13219,13 +13998,26 @@
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CK53" s="14"/>
-      <c r="CL53" s="32"/>
+      <c r="CK53" s="14">
+        <v>84</v>
+      </c>
+      <c r="CL53" s="32" t="s">
+        <v>20</v>
+      </c>
       <c r="CM53" s="15"/>
       <c r="CN53" s="33"/>
-      <c r="CO53" s="10"/>
-      <c r="CP53" s="12"/>
-      <c r="CQ53" s="11"/>
+      <c r="CO53" s="10">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="CP53" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ53" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS53" s="14"/>
       <c r="CT53" s="32"/>
       <c r="CU53" s="15"/>
@@ -13414,7 +14206,7 @@
       </c>
       <c r="BX54" s="33"/>
       <c r="BY54" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-3</v>
       </c>
       <c r="BZ54" s="12">
@@ -13444,12 +14236,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK54" s="14"/>
-      <c r="CL54" s="32"/>
+      <c r="CL54" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CM54" s="15"/>
       <c r="CN54" s="33"/>
-      <c r="CO54" s="10"/>
-      <c r="CP54" s="12"/>
-      <c r="CQ54" s="11"/>
+      <c r="CO54" s="10">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="CP54" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ54" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS54" s="14"/>
       <c r="CT54" s="32"/>
       <c r="CU54" s="15"/>
@@ -13658,7 +14461,7 @@
         <v>102147.61904713005</v>
       </c>
       <c r="BY55" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-32</v>
       </c>
       <c r="BZ55" s="12">
@@ -13692,10 +14495,27 @@
         <v>0.10401379889107165</v>
       </c>
       <c r="CK55" s="14"/>
-      <c r="CL55" s="13"/>
-      <c r="CN55" s="12"/>
-      <c r="CP55" s="12"/>
-      <c r="CQ55" s="11"/>
+      <c r="CL55" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CM55" s="10">
+        <v>75</v>
+      </c>
+      <c r="CN55" s="12">
+        <v>75446.666666359975</v>
+      </c>
+      <c r="CO55" s="10">
+        <f t="shared" si="26"/>
+        <v>-39</v>
+      </c>
+      <c r="CP55" s="12">
+        <f t="shared" si="27"/>
+        <v>-37325.71428554006</v>
+      </c>
+      <c r="CQ55" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.33098276342556177</v>
+      </c>
       <c r="CS55" s="14"/>
       <c r="CT55" s="13"/>
       <c r="CV55" s="12"/>
@@ -13902,7 +14722,7 @@
         <v>100334.28571419</v>
       </c>
       <c r="BY56" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-15</v>
       </c>
       <c r="BZ56" s="12">
@@ -13936,10 +14756,27 @@
         <v>-0.22430731554514952</v>
       </c>
       <c r="CK56" s="14"/>
-      <c r="CL56" s="13"/>
-      <c r="CN56" s="12"/>
-      <c r="CP56" s="12"/>
-      <c r="CQ56" s="11"/>
+      <c r="CL56" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CM56" s="10">
+        <v>59</v>
+      </c>
+      <c r="CN56" s="12">
+        <v>68485.714285609996</v>
+      </c>
+      <c r="CO56" s="10">
+        <f t="shared" si="26"/>
+        <v>-9</v>
+      </c>
+      <c r="CP56" s="12">
+        <f t="shared" si="27"/>
+        <v>-9342.8571428900032</v>
+      </c>
+      <c r="CQ56" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.12004405286396851</v>
+      </c>
       <c r="CS56" s="14"/>
       <c r="CT56" s="13"/>
       <c r="CV56" s="12"/>
@@ -14146,7 +14983,7 @@
         <v>131247.61904760002</v>
       </c>
       <c r="BY57" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-7</v>
       </c>
       <c r="BZ57" s="12">
@@ -14180,10 +15017,27 @@
         <v>0.22806762934483393</v>
       </c>
       <c r="CK57" s="14"/>
-      <c r="CL57" s="13"/>
-      <c r="CN57" s="12"/>
-      <c r="CP57" s="12"/>
-      <c r="CQ57" s="11"/>
+      <c r="CL57" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM57" s="10">
+        <v>11</v>
+      </c>
+      <c r="CN57" s="12">
+        <v>69895.238095230001</v>
+      </c>
+      <c r="CO57" s="10">
+        <f t="shared" si="26"/>
+        <v>-15</v>
+      </c>
+      <c r="CP57" s="12">
+        <f t="shared" si="27"/>
+        <v>-91285.714285710026</v>
+      </c>
+      <c r="CQ57" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.5663554715197523</v>
+      </c>
       <c r="CS57" s="14"/>
       <c r="CT57" s="13"/>
       <c r="CV57" s="12"/>
@@ -14390,7 +15244,7 @@
         <v>42476.190476169999</v>
       </c>
       <c r="BY58" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-11</v>
       </c>
       <c r="BZ58" s="12">
@@ -14424,10 +15278,27 @@
         <v>1.3004484304935418</v>
       </c>
       <c r="CK58" s="14"/>
-      <c r="CL58" s="13"/>
-      <c r="CN58" s="12"/>
-      <c r="CP58" s="12"/>
-      <c r="CQ58" s="11"/>
+      <c r="CL58" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CM58" s="10">
+        <v>8</v>
+      </c>
+      <c r="CN58" s="12">
+        <v>90190.47619044999</v>
+      </c>
+      <c r="CO58" s="10">
+        <f t="shared" si="26"/>
+        <v>-1</v>
+      </c>
+      <c r="CP58" s="12">
+        <f t="shared" si="27"/>
+        <v>-7523.8095238000096</v>
+      </c>
+      <c r="CQ58" s="11">
+        <f t="shared" si="28"/>
+        <v>-7.6998050682191982E-2</v>
+      </c>
       <c r="CS58" s="14"/>
       <c r="CT58" s="13"/>
       <c r="CV58" s="12"/>
@@ -14609,7 +15480,7 @@
       </c>
       <c r="BX59" s="12"/>
       <c r="BY59" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BZ59" s="12">
@@ -14638,10 +15509,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK59" s="14"/>
-      <c r="CL59" s="13"/>
+      <c r="CL59" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="CN59" s="12"/>
-      <c r="CP59" s="12"/>
-      <c r="CQ59" s="11"/>
+      <c r="CO59" s="10">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="CP59" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ59" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS59" s="14"/>
       <c r="CT59" s="13"/>
       <c r="CV59" s="12"/>
@@ -14843,7 +15726,7 @@
         <v>6290</v>
       </c>
       <c r="BY60" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="BZ60" s="12">
@@ -14877,10 +15760,22 @@
         <v>0.3958664546899841</v>
       </c>
       <c r="CK60" s="14"/>
-      <c r="CL60" s="13"/>
+      <c r="CL60" s="13" t="s">
+        <v>5</v>
+      </c>
       <c r="CN60" s="12"/>
-      <c r="CP60" s="12"/>
-      <c r="CQ60" s="11"/>
+      <c r="CO60" s="10">
+        <f t="shared" si="26"/>
+        <v>-2</v>
+      </c>
+      <c r="CP60" s="12">
+        <f t="shared" si="27"/>
+        <v>-8780</v>
+      </c>
+      <c r="CQ60" s="11">
+        <f t="shared" si="28"/>
+        <v>-1</v>
+      </c>
       <c r="CS60" s="14"/>
       <c r="CT60" s="13"/>
       <c r="CV60" s="12"/>
@@ -15087,7 +15982,7 @@
         <v>83142.857142840003</v>
       </c>
       <c r="BY61" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-3</v>
       </c>
       <c r="BZ61" s="12">
@@ -15121,10 +16016,27 @@
         <v>9.62199312714975E-2</v>
       </c>
       <c r="CK61" s="14"/>
-      <c r="CL61" s="13"/>
-      <c r="CN61" s="12"/>
-      <c r="CP61" s="12"/>
-      <c r="CQ61" s="11"/>
+      <c r="CL61" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CM61" s="10">
+        <v>1</v>
+      </c>
+      <c r="CN61" s="12">
+        <v>27523.809523799999</v>
+      </c>
+      <c r="CO61" s="10">
+        <f t="shared" si="26"/>
+        <v>-2</v>
+      </c>
+      <c r="CP61" s="12">
+        <f t="shared" si="27"/>
+        <v>-63619.047619040008</v>
+      </c>
+      <c r="CQ61" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.69801462904915956</v>
+      </c>
       <c r="CS61" s="14"/>
       <c r="CT61" s="13"/>
       <c r="CV61" s="12"/>
@@ -15331,7 +16243,7 @@
         <v>217142.85714284002</v>
       </c>
       <c r="BY62" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-6</v>
       </c>
       <c r="BZ62" s="12">
@@ -15365,10 +16277,27 @@
         <v>0.75350877192980292</v>
       </c>
       <c r="CK62" s="14"/>
-      <c r="CL62" s="13"/>
-      <c r="CN62" s="12"/>
-      <c r="CP62" s="12"/>
-      <c r="CQ62" s="11"/>
+      <c r="CL62" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CM62" s="10">
+        <v>7</v>
+      </c>
+      <c r="CN62" s="12">
+        <v>91333.333333310002</v>
+      </c>
+      <c r="CO62" s="10">
+        <f t="shared" si="26"/>
+        <v>-22</v>
+      </c>
+      <c r="CP62" s="12">
+        <f t="shared" si="27"/>
+        <v>-289428.57142856007</v>
+      </c>
+      <c r="CQ62" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.76013006503255576</v>
+      </c>
       <c r="CS62" s="14"/>
       <c r="CT62" s="13"/>
       <c r="CV62" s="12"/>
@@ -15575,7 +16504,7 @@
         <v>456340.95238093007</v>
       </c>
       <c r="BY63" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-9</v>
       </c>
       <c r="BZ63" s="12">
@@ -15609,10 +16538,27 @@
         <v>0.28391887435876384</v>
       </c>
       <c r="CK63" s="14"/>
-      <c r="CL63" s="13"/>
-      <c r="CN63" s="12"/>
-      <c r="CP63" s="12"/>
-      <c r="CQ63" s="11"/>
+      <c r="CL63" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CM63" s="10">
+        <v>20</v>
+      </c>
+      <c r="CN63" s="12">
+        <v>659047.61904759007</v>
+      </c>
+      <c r="CO63" s="10">
+        <f t="shared" si="26"/>
+        <v>2</v>
+      </c>
+      <c r="CP63" s="12">
+        <f t="shared" si="27"/>
+        <v>73142.85714286007</v>
+      </c>
+      <c r="CQ63" s="11">
+        <f t="shared" si="28"/>
+        <v>0.12483745123538241</v>
+      </c>
       <c r="CS63" s="14"/>
       <c r="CT63" s="13"/>
       <c r="CV63" s="12"/>
@@ -15820,7 +16766,7 @@
         <v>1139122.3809517003</v>
       </c>
       <c r="BY64" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-82</v>
       </c>
       <c r="BZ64" s="28">
@@ -15853,13 +16799,28 @@
         <f t="shared" si="25"/>
         <v>0.33092434986519093</v>
       </c>
-      <c r="CK64" s="9"/>
+      <c r="CK64" s="9" t="s">
+        <v>1</v>
+      </c>
       <c r="CL64" s="9"/>
-      <c r="CM64" s="8"/>
-      <c r="CN64" s="7"/>
-      <c r="CO64" s="27"/>
-      <c r="CP64" s="28"/>
-      <c r="CQ64" s="29"/>
+      <c r="CM64" s="8">
+        <v>181</v>
+      </c>
+      <c r="CN64" s="7">
+        <v>1081922.8571423502</v>
+      </c>
+      <c r="CO64" s="27">
+        <f t="shared" si="26"/>
+        <v>-88</v>
+      </c>
+      <c r="CP64" s="28">
+        <f t="shared" si="27"/>
+        <v>-434162.85714267986</v>
+      </c>
+      <c r="CQ64" s="29">
+        <f t="shared" si="28"/>
+        <v>-0.28637091758853916</v>
+      </c>
       <c r="CS64" s="9"/>
       <c r="CT64" s="9"/>
       <c r="CU64" s="8"/>
@@ -16069,7 +17030,7 @@
         <v>11122184.761900868</v>
       </c>
       <c r="BY65" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-669</v>
       </c>
       <c r="BZ65" s="5">
@@ -16102,13 +17063,28 @@
         <f t="shared" si="25"/>
         <v>0.92062826128569275</v>
       </c>
-      <c r="CK65" s="4"/>
+      <c r="CK65" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="CL65" s="4"/>
-      <c r="CM65" s="3"/>
-      <c r="CN65" s="2"/>
-      <c r="CO65" s="6"/>
-      <c r="CP65" s="5"/>
-      <c r="CQ65" s="30"/>
+      <c r="CM65" s="3">
+        <v>2060</v>
+      </c>
+      <c r="CN65" s="2">
+        <v>19139967.142853197</v>
+      </c>
+      <c r="CO65" s="6">
+        <f t="shared" si="26"/>
+        <v>-245</v>
+      </c>
+      <c r="CP65" s="5">
+        <f t="shared" si="27"/>
+        <v>-2221615.2380946949</v>
+      </c>
+      <c r="CQ65" s="30">
+        <f t="shared" si="28"/>
+        <v>-0.10400049951712022</v>
+      </c>
       <c r="CS65" s="4"/>
       <c r="CT65" s="4"/>
       <c r="CU65" s="3"/>
@@ -16125,7 +17101,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="109" operator="containsText" id="{84E91190-11E8-AE4A-9A8E-E0B241655290}">
+          <x14:cfRule type="containsText" priority="110" operator="containsText" id="{84E91190-11E8-AE4A-9A8E-E0B241655290}">
             <xm:f>NOT(ISERROR(SEARCH("-",E7)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16137,7 +17113,7 @@
           <xm:sqref>E7:G65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{CCFCC0A6-CB12-AB49-93FE-0A85BBD26278}">
+          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{CCFCC0A6-CB12-AB49-93FE-0A85BBD26278}">
             <xm:f>NOT(ISERROR(SEARCH("-",M5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16149,7 +17125,7 @@
           <xm:sqref>M5:O65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{77E3898A-1BFA-D640-9BA9-3433EFE4A95F}">
+          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{77E3898A-1BFA-D640-9BA9-3433EFE4A95F}">
             <xm:f>NOT(ISERROR(SEARCH("-",U5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16161,7 +17137,7 @@
           <xm:sqref>U5:W65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{D9706009-D5AD-2741-B804-EFED1C726C5E}">
+          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{D9706009-D5AD-2741-B804-EFED1C726C5E}">
             <xm:f>NOT(ISERROR(SEARCH("-",AC5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16173,7 +17149,7 @@
           <xm:sqref>AC5:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{0ED7C4E6-BDE3-3246-BC08-84A539C7A360}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{0ED7C4E6-BDE3-3246-BC08-84A539C7A360}">
             <xm:f>NOT(ISERROR(SEARCH("-",AJ5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16185,7 +17161,7 @@
           <xm:sqref>AJ5:AM65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{6F25B2E1-166C-A14E-8434-CB8394590228}">
+          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{6F25B2E1-166C-A14E-8434-CB8394590228}">
             <xm:f>NOT(ISERROR(SEARCH("-",AS5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16197,7 +17173,7 @@
           <xm:sqref>AS5:AU65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{B91A5596-3F8E-6648-95BA-8781A9ECC29E}">
+          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{B91A5596-3F8E-6648-95BA-8781A9ECC29E}">
             <xm:f>NOT(ISERROR(SEARCH("-",BA5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16209,7 +17185,7 @@
           <xm:sqref>BA5:BC65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{E93B6814-05C6-8F46-A383-0AA3B037BA87}">
+          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{E93B6814-05C6-8F46-A383-0AA3B037BA87}">
             <xm:f>NOT(ISERROR(SEARCH("-",BI5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16221,7 +17197,7 @@
           <xm:sqref>BI5:BK65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{C5C117FA-A310-C347-B988-7B736BE0F8CB}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{C5C117FA-A310-C347-B988-7B736BE0F8CB}">
             <xm:f>NOT(ISERROR(SEARCH("-",BQ5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16233,7 +17209,7 @@
           <xm:sqref>BQ5:BS65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{8AD91545-A880-0646-B88D-4021F4CD6A07}">
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{8AD91545-A880-0646-B88D-4021F4CD6A07}">
             <xm:f>NOT(ISERROR(SEARCH("-",BY5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16245,7 +17221,7 @@
           <xm:sqref>BY5:CA65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{6A1FAD57-8B56-AD43-BC86-FE7B8B27DAC3}">
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{6A1FAD57-8B56-AD43-BC86-FE7B8B27DAC3}">
             <xm:f>NOT(ISERROR(SEARCH("-",CG5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16257,7 +17233,7 @@
           <xm:sqref>CG5:CI65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{00C895F4-D5E3-F04E-93CB-E795A6DC8C2F}">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{F04093BB-F5FD-F043-B0A6-2D2AB47A2695}">
             <xm:f>NOT(ISERROR(SEARCH("-",CO5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16269,7 +17245,7 @@
           <xm:sqref>CO5:CQ65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{4126E041-CCDA-FB44-8F91-ACB733D36FB3}">
+          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{4126E041-CCDA-FB44-8F91-ACB733D36FB3}">
             <xm:f>NOT(ISERROR(SEARCH("-",CW5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>

--- a/data/quarterly/FY26Q2.xlsx
+++ b/data/quarterly/FY26Q2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/bystore/data/quarterly/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE836E5-63B5-A549-AD2F-CD6D457EF9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8FAFBB-653C-5946-AC08-BEB442DA2EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5400" yWindow="680" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -1943,10 +1943,13 @@
       <c r="CL6" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="CM6" s="15">
+        <v>1</v>
+      </c>
       <c r="CN6" s="33"/>
       <c r="CO6" s="10">
         <f t="shared" si="26"/>
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="CP6" s="12">
         <f t="shared" si="27"/>

--- a/data/quarterly/FY26Q2.xlsx
+++ b/data/quarterly/FY26Q2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/bystore/data/quarterly/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8FAFBB-653C-5946-AC08-BEB442DA2EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793FB02E-9673-9447-A447-22229F527E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="680" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="5640" yWindow="1520" windowWidth="19540" windowHeight="20180" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="48">
   <si>
     <t>總計</t>
   </si>
@@ -236,6 +236,14 @@
   </si>
   <si>
     <t>03/15~03/21</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q2W13</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03/22~03/28</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -567,7 +575,12 @@
     <cellStyle name="一般 2" xfId="2" xr:uid="{0CB5398D-811F-454E-A670-53B654D1D081}"/>
     <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1095,7 +1108,11 @@
       </c>
       <c r="CL1" s="26"/>
       <c r="CN1" s="25"/>
-      <c r="CS1" s="26"/>
+      <c r="CS1" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="CT1" s="26"/>
+      <c r="CV1" s="25"/>
     </row>
     <row r="2" spans="1:103" s="20" customFormat="1" ht="18">
       <c r="A2" s="23" t="s">
@@ -1176,7 +1193,9 @@
       <c r="CO2" s="21"/>
       <c r="CP2" s="21"/>
       <c r="CQ2" s="21"/>
-      <c r="CS2" s="22"/>
+      <c r="CS2" s="20" t="s">
+        <v>47</v>
+      </c>
       <c r="CT2" s="21"/>
       <c r="CV2" s="21"/>
       <c r="CW2" s="21"/>
@@ -1444,13 +1463,27 @@
       <c r="CQ4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="CS4" s="19"/>
-      <c r="CT4" s="19"/>
-      <c r="CU4" s="18"/>
-      <c r="CV4" s="17"/>
-      <c r="CW4" s="16"/>
-      <c r="CX4" s="16"/>
-      <c r="CY4" s="16"/>
+      <c r="CS4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="CT4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="CU4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="CV4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="CW4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="CX4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="CY4" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" spans="1:103" s="39" customFormat="1" ht="22" customHeight="1">
       <c r="A5" s="14">
@@ -1720,13 +1753,28 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CR5" s="38"/>
-      <c r="CS5" s="14"/>
-      <c r="CT5" s="32"/>
-      <c r="CU5" s="15"/>
+      <c r="CS5" s="14">
+        <v>75</v>
+      </c>
+      <c r="CT5" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CU5" s="15">
+        <v>6354</v>
+      </c>
       <c r="CV5" s="33"/>
-      <c r="CW5" s="10"/>
-      <c r="CX5" s="12"/>
-      <c r="CY5" s="11"/>
+      <c r="CW5" s="10">
+        <f t="shared" ref="CW5:CW65" si="29">CU5-CM5</f>
+        <v>272</v>
+      </c>
+      <c r="CX5" s="12">
+        <f t="shared" ref="CX5:CX65" si="30">CV5-CN5</f>
+        <v>0</v>
+      </c>
+      <c r="CY5" s="11" t="e">
+        <f t="shared" ref="CY5:CY65" si="31">(CV5-CN5)/CN5</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="6" spans="1:103" s="15" customFormat="1" ht="22" customHeight="1">
       <c r="A6" s="14"/>
@@ -1944,12 +1992,12 @@
         <v>21</v>
       </c>
       <c r="CM6" s="15">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="CN6" s="33"/>
       <c r="CO6" s="10">
         <f t="shared" si="26"/>
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="CP6" s="12">
         <f t="shared" si="27"/>
@@ -1960,11 +2008,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CS6" s="14"/>
-      <c r="CT6" s="32"/>
+      <c r="CT6" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CV6" s="33"/>
-      <c r="CW6" s="10"/>
-      <c r="CX6" s="12"/>
-      <c r="CY6" s="11"/>
+      <c r="CW6" s="10">
+        <f t="shared" si="29"/>
+        <v>-15</v>
+      </c>
+      <c r="CX6" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY6" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="7" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A7" s="14"/>
@@ -2222,10 +2281,27 @@
         <v>-0.18246126353882261</v>
       </c>
       <c r="CS7" s="14"/>
-      <c r="CT7" s="13"/>
-      <c r="CV7" s="12"/>
-      <c r="CX7" s="12"/>
-      <c r="CY7" s="11"/>
+      <c r="CT7" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CU7" s="10">
+        <v>197</v>
+      </c>
+      <c r="CV7" s="12">
+        <v>210633.33333257007</v>
+      </c>
+      <c r="CW7" s="10">
+        <f t="shared" si="29"/>
+        <v>26</v>
+      </c>
+      <c r="CX7" s="12">
+        <f t="shared" si="30"/>
+        <v>31993.333333280141</v>
+      </c>
+      <c r="CY7" s="11">
+        <f t="shared" si="31"/>
+        <v>0.17909389461155012</v>
+      </c>
     </row>
     <row r="8" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A8" s="14"/>
@@ -2483,10 +2559,27 @@
         <v>-0.13345697379771318</v>
       </c>
       <c r="CS8" s="14"/>
-      <c r="CT8" s="13"/>
-      <c r="CV8" s="12"/>
-      <c r="CX8" s="12"/>
-      <c r="CY8" s="11"/>
+      <c r="CT8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CU8" s="10">
+        <v>237</v>
+      </c>
+      <c r="CV8" s="12">
+        <v>348669.52380933991</v>
+      </c>
+      <c r="CW8" s="10">
+        <f t="shared" si="29"/>
+        <v>20</v>
+      </c>
+      <c r="CX8" s="12">
+        <f t="shared" si="30"/>
+        <v>105705.71428566991</v>
+      </c>
+      <c r="CY8" s="11">
+        <f t="shared" si="31"/>
+        <v>0.43506773495569451</v>
+      </c>
     </row>
     <row r="9" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A9" s="14"/>
@@ -2744,10 +2837,27 @@
         <v>-8.5987565758025214E-2</v>
       </c>
       <c r="CS9" s="14"/>
-      <c r="CT9" s="13"/>
-      <c r="CV9" s="12"/>
-      <c r="CX9" s="12"/>
-      <c r="CY9" s="11"/>
+      <c r="CT9" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CU9" s="10">
+        <v>72</v>
+      </c>
+      <c r="CV9" s="12">
+        <v>452887.61904760997</v>
+      </c>
+      <c r="CW9" s="10">
+        <f t="shared" si="29"/>
+        <v>2</v>
+      </c>
+      <c r="CX9" s="12">
+        <f t="shared" si="30"/>
+        <v>-2159.9999999899883</v>
+      </c>
+      <c r="CY9" s="11">
+        <f t="shared" si="31"/>
+        <v>-4.7467559648170423E-3</v>
+      </c>
     </row>
     <row r="10" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A10" s="14"/>
@@ -3005,10 +3115,27 @@
         <v>-7.407407407409039E-2</v>
       </c>
       <c r="CS10" s="14"/>
-      <c r="CT10" s="13"/>
-      <c r="CV10" s="12"/>
-      <c r="CX10" s="12"/>
-      <c r="CY10" s="11"/>
+      <c r="CT10" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CU10" s="10">
+        <v>54</v>
+      </c>
+      <c r="CV10" s="12">
+        <v>929142.85714277998</v>
+      </c>
+      <c r="CW10" s="10">
+        <f t="shared" si="29"/>
+        <v>19</v>
+      </c>
+      <c r="CX10" s="12">
+        <f t="shared" si="30"/>
+        <v>445809.52380951995</v>
+      </c>
+      <c r="CY10" s="11">
+        <f t="shared" si="31"/>
+        <v>0.92236453201983637</v>
+      </c>
     </row>
     <row r="11" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A11" s="14"/>
@@ -3236,10 +3363,27 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CS11" s="14"/>
-      <c r="CT11" s="13"/>
-      <c r="CV11" s="12"/>
-      <c r="CX11" s="12"/>
-      <c r="CY11" s="11"/>
+      <c r="CT11" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="CU11" s="10">
+        <v>1</v>
+      </c>
+      <c r="CV11" s="12">
+        <v>8857.1428571399993</v>
+      </c>
+      <c r="CW11" s="10">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="CX11" s="12">
+        <f t="shared" si="30"/>
+        <v>8857.1428571399993</v>
+      </c>
+      <c r="CY11" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="12" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A12" s="14"/>
@@ -3497,10 +3641,27 @@
         <v>0.74442025040827431</v>
       </c>
       <c r="CS12" s="14"/>
-      <c r="CT12" s="13"/>
-      <c r="CV12" s="12"/>
-      <c r="CX12" s="12"/>
-      <c r="CY12" s="11"/>
+      <c r="CT12" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CU12" s="10">
+        <v>8</v>
+      </c>
+      <c r="CV12" s="12">
+        <v>46420</v>
+      </c>
+      <c r="CW12" s="10">
+        <f t="shared" si="29"/>
+        <v>-3</v>
+      </c>
+      <c r="CX12" s="12">
+        <f t="shared" si="30"/>
+        <v>-17670</v>
+      </c>
+      <c r="CY12" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.27570603838352314</v>
+      </c>
     </row>
     <row r="13" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A13" s="14"/>
@@ -3758,10 +3919,27 @@
         <v>-0.50447452009391824</v>
       </c>
       <c r="CS13" s="14"/>
-      <c r="CT13" s="13"/>
-      <c r="CV13" s="12"/>
-      <c r="CX13" s="12"/>
-      <c r="CY13" s="11"/>
+      <c r="CT13" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CU13" s="10">
+        <v>5</v>
+      </c>
+      <c r="CV13" s="12">
+        <v>275423.80952379998</v>
+      </c>
+      <c r="CW13" s="10">
+        <f t="shared" si="29"/>
+        <v>-3</v>
+      </c>
+      <c r="CX13" s="12">
+        <f t="shared" si="30"/>
+        <v>-66299.999999970081</v>
+      </c>
+      <c r="CY13" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.19401633176326363</v>
+      </c>
     </row>
     <row r="14" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A14" s="14"/>
@@ -4019,10 +4197,27 @@
         <v>-0.44086935405535715</v>
       </c>
       <c r="CS14" s="14"/>
-      <c r="CT14" s="13"/>
-      <c r="CV14" s="12"/>
-      <c r="CX14" s="12"/>
-      <c r="CY14" s="11"/>
+      <c r="CT14" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CU14" s="10">
+        <v>89</v>
+      </c>
+      <c r="CV14" s="12">
+        <v>1702285.7142856203</v>
+      </c>
+      <c r="CW14" s="10">
+        <f t="shared" si="29"/>
+        <v>65</v>
+      </c>
+      <c r="CX14" s="12">
+        <f t="shared" si="30"/>
+        <v>1263714.2857142303</v>
+      </c>
+      <c r="CY14" s="11">
+        <f t="shared" si="31"/>
+        <v>2.8814332247558272</v>
+      </c>
     </row>
     <row r="15" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A15" s="14"/>
@@ -4280,10 +4475,27 @@
         <v>-0.32080884629566497</v>
       </c>
       <c r="CS15" s="14"/>
-      <c r="CT15" s="13"/>
-      <c r="CV15" s="12"/>
-      <c r="CX15" s="12"/>
-      <c r="CY15" s="11"/>
+      <c r="CT15" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CU15" s="10">
+        <v>333</v>
+      </c>
+      <c r="CV15" s="12">
+        <v>13040666.666666551</v>
+      </c>
+      <c r="CW15" s="10">
+        <f t="shared" si="29"/>
+        <v>218</v>
+      </c>
+      <c r="CX15" s="12">
+        <f t="shared" si="30"/>
+        <v>8881142.857142821</v>
+      </c>
+      <c r="CY15" s="11">
+        <f t="shared" si="31"/>
+        <v>2.1351345163137125</v>
+      </c>
     </row>
     <row r="16" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A16" s="9" t="s">
@@ -4541,13 +4753,28 @@
         <f t="shared" si="28"/>
         <v>-0.30477520096695548</v>
       </c>
-      <c r="CS16" s="9"/>
+      <c r="CS16" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="CT16" s="9"/>
-      <c r="CU16" s="8"/>
-      <c r="CV16" s="7"/>
-      <c r="CW16" s="27"/>
-      <c r="CX16" s="28"/>
-      <c r="CY16" s="29"/>
+      <c r="CU16" s="8">
+        <v>996</v>
+      </c>
+      <c r="CV16" s="7">
+        <v>17014986.666665412</v>
+      </c>
+      <c r="CW16" s="27">
+        <f t="shared" si="29"/>
+        <v>345</v>
+      </c>
+      <c r="CX16" s="28">
+        <f t="shared" si="30"/>
+        <v>10651092.857142702</v>
+      </c>
+      <c r="CY16" s="29">
+        <f t="shared" si="31"/>
+        <v>1.6736754534157647</v>
+      </c>
     </row>
     <row r="17" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A17" s="14">
@@ -4804,13 +5031,28 @@
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CS17" s="14"/>
-      <c r="CT17" s="32"/>
-      <c r="CU17" s="15"/>
+      <c r="CS17" s="14">
+        <v>76</v>
+      </c>
+      <c r="CT17" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CU17" s="15">
+        <v>4216</v>
+      </c>
       <c r="CV17" s="33"/>
-      <c r="CW17" s="10"/>
-      <c r="CX17" s="12"/>
-      <c r="CY17" s="11"/>
+      <c r="CW17" s="10">
+        <f t="shared" si="29"/>
+        <v>-1133</v>
+      </c>
+      <c r="CX17" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY17" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="18" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A18" s="14"/>
@@ -5027,11 +5269,13 @@
       <c r="CL18" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CM18" s="15"/>
+      <c r="CM18" s="15">
+        <v>15</v>
+      </c>
       <c r="CN18" s="33"/>
       <c r="CO18" s="10">
         <f t="shared" si="26"/>
-        <v>-13</v>
+        <v>2</v>
       </c>
       <c r="CP18" s="12">
         <f t="shared" si="27"/>
@@ -5042,12 +5286,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CS18" s="14"/>
-      <c r="CT18" s="32"/>
+      <c r="CT18" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CU18" s="15"/>
       <c r="CV18" s="33"/>
-      <c r="CW18" s="10"/>
-      <c r="CX18" s="12"/>
-      <c r="CY18" s="11"/>
+      <c r="CW18" s="10">
+        <f t="shared" si="29"/>
+        <v>-15</v>
+      </c>
+      <c r="CX18" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY18" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="19" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A19" s="14"/>
@@ -5305,10 +5560,27 @@
         <v>7.4207219828554896E-2</v>
       </c>
       <c r="CS19" s="14"/>
-      <c r="CT19" s="13"/>
-      <c r="CV19" s="12"/>
-      <c r="CX19" s="12"/>
-      <c r="CY19" s="11"/>
+      <c r="CT19" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CU19" s="10">
+        <v>181</v>
+      </c>
+      <c r="CV19" s="12">
+        <v>194270.47618971989</v>
+      </c>
+      <c r="CW19" s="10">
+        <f t="shared" si="29"/>
+        <v>-30</v>
+      </c>
+      <c r="CX19" s="12">
+        <f t="shared" si="30"/>
+        <v>-37948.571428480151</v>
+      </c>
+      <c r="CY19" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.16341713488926543</v>
+      </c>
     </row>
     <row r="20" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A20" s="14"/>
@@ -5566,10 +5838,27 @@
         <v>-0.28636093542440028</v>
       </c>
       <c r="CS20" s="14"/>
-      <c r="CT20" s="13"/>
-      <c r="CV20" s="12"/>
-      <c r="CX20" s="12"/>
-      <c r="CY20" s="11"/>
+      <c r="CT20" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CU20" s="10">
+        <v>150</v>
+      </c>
+      <c r="CV20" s="12">
+        <v>180562.85714273</v>
+      </c>
+      <c r="CW20" s="10">
+        <f t="shared" si="29"/>
+        <v>-69</v>
+      </c>
+      <c r="CX20" s="12">
+        <f t="shared" si="30"/>
+        <v>-37903.809523820004</v>
+      </c>
+      <c r="CY20" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.17349928070113019</v>
+      </c>
     </row>
     <row r="21" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A21" s="14"/>
@@ -5827,10 +6116,27 @@
         <v>0.12521337746037256</v>
       </c>
       <c r="CS21" s="14"/>
-      <c r="CT21" s="13"/>
-      <c r="CV21" s="12"/>
-      <c r="CX21" s="12"/>
-      <c r="CY21" s="11"/>
+      <c r="CT21" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CU21" s="10">
+        <v>58</v>
+      </c>
+      <c r="CV21" s="12">
+        <v>362304.76190474001</v>
+      </c>
+      <c r="CW21" s="10">
+        <f t="shared" si="29"/>
+        <v>-3</v>
+      </c>
+      <c r="CX21" s="12">
+        <f t="shared" si="30"/>
+        <v>-6829.5238095199456</v>
+      </c>
+      <c r="CY21" s="11">
+        <f t="shared" si="31"/>
+        <v>-1.8501461592236257E-2</v>
+      </c>
     </row>
     <row r="22" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A22" s="14"/>
@@ -6088,10 +6394,27 @@
         <v>0.23266351457841633</v>
       </c>
       <c r="CS22" s="14"/>
-      <c r="CT22" s="13"/>
-      <c r="CV22" s="12"/>
-      <c r="CX22" s="12"/>
-      <c r="CY22" s="11"/>
+      <c r="CT22" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CU22" s="10">
+        <v>31</v>
+      </c>
+      <c r="CV22" s="12">
+        <v>380857.14285708003</v>
+      </c>
+      <c r="CW22" s="10">
+        <f t="shared" si="29"/>
+        <v>-17</v>
+      </c>
+      <c r="CX22" s="12">
+        <f t="shared" si="30"/>
+        <v>-215047.61904761003</v>
+      </c>
+      <c r="CY22" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.36087581908265581</v>
+      </c>
     </row>
     <row r="23" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A23" s="14"/>
@@ -6339,10 +6662,27 @@
         <v>6.8459057071999236</v>
       </c>
       <c r="CS23" s="14"/>
-      <c r="CT23" s="13"/>
-      <c r="CV23" s="12"/>
-      <c r="CX23" s="12"/>
-      <c r="CY23" s="11"/>
+      <c r="CT23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="CU23" s="10">
+        <v>1</v>
+      </c>
+      <c r="CV23" s="12">
+        <v>8857.1428571399993</v>
+      </c>
+      <c r="CW23" s="10">
+        <f t="shared" si="29"/>
+        <v>-15</v>
+      </c>
+      <c r="CX23" s="12">
+        <f t="shared" si="30"/>
+        <v>-81482.857142859997</v>
+      </c>
+      <c r="CY23" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.90195768367124196</v>
+      </c>
     </row>
     <row r="24" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A24" s="14"/>
@@ -6595,10 +6935,27 @@
         <v>-1</v>
       </c>
       <c r="CS24" s="14"/>
-      <c r="CT24" s="13"/>
-      <c r="CV24" s="12"/>
-      <c r="CX24" s="12"/>
-      <c r="CY24" s="11"/>
+      <c r="CT24" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CU24" s="10">
+        <v>10</v>
+      </c>
+      <c r="CV24" s="12">
+        <v>62700</v>
+      </c>
+      <c r="CW24" s="10">
+        <f t="shared" si="29"/>
+        <v>10</v>
+      </c>
+      <c r="CX24" s="12">
+        <f t="shared" si="30"/>
+        <v>62700</v>
+      </c>
+      <c r="CY24" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="25" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A25" s="14"/>
@@ -6856,10 +7213,27 @@
         <v>-0.5849775498930726</v>
       </c>
       <c r="CS25" s="14"/>
-      <c r="CT25" s="13"/>
-      <c r="CV25" s="12"/>
-      <c r="CX25" s="12"/>
-      <c r="CY25" s="11"/>
+      <c r="CT25" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CU25" s="10">
+        <v>5</v>
+      </c>
+      <c r="CV25" s="12">
+        <v>228757.14285713001</v>
+      </c>
+      <c r="CW25" s="10">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="CX25" s="12">
+        <f t="shared" si="30"/>
+        <v>89228.571428569994</v>
+      </c>
+      <c r="CY25" s="11">
+        <f t="shared" si="31"/>
+        <v>0.63950035834958641</v>
+      </c>
     </row>
     <row r="26" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A26" s="14"/>
@@ -7117,10 +7491,27 @@
         <v>3.4012563199060437E-2</v>
       </c>
       <c r="CS26" s="14"/>
-      <c r="CT26" s="13"/>
-      <c r="CV26" s="12"/>
-      <c r="CX26" s="12"/>
-      <c r="CY26" s="11"/>
+      <c r="CT26" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CU26" s="10">
+        <v>36</v>
+      </c>
+      <c r="CV26" s="12">
+        <v>573428.57142852002</v>
+      </c>
+      <c r="CW26" s="10">
+        <f t="shared" si="29"/>
+        <v>-3</v>
+      </c>
+      <c r="CX26" s="12">
+        <f t="shared" si="30"/>
+        <v>-69333.333333329996</v>
+      </c>
+      <c r="CY26" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.10786783227145162</v>
+      </c>
     </row>
     <row r="27" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A27" s="14"/>
@@ -7378,10 +7769,27 @@
         <v>0.32529132096579144</v>
       </c>
       <c r="CS27" s="14"/>
-      <c r="CT27" s="13"/>
-      <c r="CV27" s="12"/>
-      <c r="CX27" s="12"/>
-      <c r="CY27" s="11"/>
+      <c r="CT27" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CU27" s="10">
+        <v>126</v>
+      </c>
+      <c r="CV27" s="12">
+        <v>4788952.38095228</v>
+      </c>
+      <c r="CW27" s="10">
+        <f t="shared" si="29"/>
+        <v>-62</v>
+      </c>
+      <c r="CX27" s="12">
+        <f t="shared" si="30"/>
+        <v>-1980761.9047619095</v>
+      </c>
+      <c r="CY27" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.29259165470865123</v>
+      </c>
     </row>
     <row r="28" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A28" s="9" t="s">
@@ -7639,13 +8047,28 @@
         <f t="shared" si="28"/>
         <v>0.20521532403134726</v>
       </c>
-      <c r="CS28" s="9"/>
+      <c r="CS28" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="CT28" s="9"/>
-      <c r="CU28" s="8"/>
-      <c r="CV28" s="7"/>
-      <c r="CW28" s="27"/>
-      <c r="CX28" s="28"/>
-      <c r="CY28" s="29"/>
+      <c r="CU28" s="8">
+        <v>598</v>
+      </c>
+      <c r="CV28" s="7">
+        <v>6780690.4761893395</v>
+      </c>
+      <c r="CW28" s="27">
+        <f t="shared" si="29"/>
+        <v>-189</v>
+      </c>
+      <c r="CX28" s="28">
+        <f t="shared" si="30"/>
+        <v>-2277379.047618961</v>
+      </c>
+      <c r="CY28" s="29">
+        <f t="shared" si="31"/>
+        <v>-0.25141991255786678</v>
+      </c>
     </row>
     <row r="29" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A29" s="14">
@@ -7902,13 +8325,28 @@
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CS29" s="14"/>
-      <c r="CT29" s="32"/>
-      <c r="CU29" s="15"/>
+      <c r="CS29" s="14">
+        <v>77</v>
+      </c>
+      <c r="CT29" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CU29" s="15">
+        <v>3195</v>
+      </c>
       <c r="CV29" s="33"/>
-      <c r="CW29" s="10"/>
-      <c r="CX29" s="12"/>
-      <c r="CY29" s="11"/>
+      <c r="CW29" s="10">
+        <f t="shared" si="29"/>
+        <v>-244</v>
+      </c>
+      <c r="CX29" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY29" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="30" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A30" s="14"/>
@@ -8125,11 +8563,13 @@
       <c r="CL30" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CM30" s="15"/>
+      <c r="CM30" s="15">
+        <v>5</v>
+      </c>
       <c r="CN30" s="33"/>
       <c r="CO30" s="10">
         <f t="shared" si="26"/>
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="CP30" s="12">
         <f t="shared" si="27"/>
@@ -8140,12 +8580,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CS30" s="14"/>
-      <c r="CT30" s="32"/>
+      <c r="CT30" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CU30" s="15"/>
       <c r="CV30" s="33"/>
-      <c r="CW30" s="10"/>
-      <c r="CX30" s="12"/>
-      <c r="CY30" s="11"/>
+      <c r="CW30" s="10">
+        <f t="shared" si="29"/>
+        <v>-5</v>
+      </c>
+      <c r="CX30" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY30" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="31" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A31" s="14"/>
@@ -8403,10 +8854,27 @@
         <v>-0.14127742830228468</v>
       </c>
       <c r="CS31" s="14"/>
-      <c r="CT31" s="13"/>
-      <c r="CV31" s="12"/>
-      <c r="CX31" s="12"/>
-      <c r="CY31" s="11"/>
+      <c r="CT31" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CU31" s="10">
+        <v>115</v>
+      </c>
+      <c r="CV31" s="12">
+        <v>98313.333332900031</v>
+      </c>
+      <c r="CW31" s="10">
+        <f t="shared" si="29"/>
+        <v>44</v>
+      </c>
+      <c r="CX31" s="12">
+        <f t="shared" si="30"/>
+        <v>32268.571428450014</v>
+      </c>
+      <c r="CY31" s="11">
+        <f t="shared" si="31"/>
+        <v>0.48858638441507951</v>
+      </c>
     </row>
     <row r="32" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A32" s="14"/>
@@ -8664,10 +9132,27 @@
         <v>-5.4720000000067853E-2</v>
       </c>
       <c r="CS32" s="14"/>
-      <c r="CT32" s="13"/>
-      <c r="CV32" s="12"/>
-      <c r="CX32" s="12"/>
-      <c r="CY32" s="11"/>
+      <c r="CT32" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CU32" s="10">
+        <v>54</v>
+      </c>
+      <c r="CV32" s="12">
+        <v>61199.999999920008</v>
+      </c>
+      <c r="CW32" s="10">
+        <f t="shared" si="29"/>
+        <v>-23</v>
+      </c>
+      <c r="CX32" s="12">
+        <f t="shared" si="30"/>
+        <v>-17573.333333309987</v>
+      </c>
+      <c r="CY32" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.22308733920107957</v>
+      </c>
     </row>
     <row r="33" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A33" s="14"/>
@@ -8925,10 +9410,27 @@
         <v>0.53199222381885614</v>
       </c>
       <c r="CS33" s="14"/>
-      <c r="CT33" s="13"/>
-      <c r="CV33" s="12"/>
-      <c r="CX33" s="12"/>
-      <c r="CY33" s="11"/>
+      <c r="CT33" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CU33" s="10">
+        <v>14</v>
+      </c>
+      <c r="CV33" s="12">
+        <v>84748.571428559997</v>
+      </c>
+      <c r="CW33" s="10">
+        <f t="shared" si="29"/>
+        <v>-11</v>
+      </c>
+      <c r="CX33" s="12">
+        <f t="shared" si="30"/>
+        <v>-87870.476190480011</v>
+      </c>
+      <c r="CY33" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.50904275862073423</v>
+      </c>
     </row>
     <row r="34" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A34" s="14"/>
@@ -9186,10 +9688,27 @@
         <v>0.18561278863225966</v>
       </c>
       <c r="CS34" s="14"/>
-      <c r="CT34" s="13"/>
-      <c r="CV34" s="12"/>
-      <c r="CX34" s="12"/>
-      <c r="CY34" s="11"/>
+      <c r="CT34" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CU34" s="10">
+        <v>8</v>
+      </c>
+      <c r="CV34" s="12">
+        <v>124952.38095235001</v>
+      </c>
+      <c r="CW34" s="10">
+        <f t="shared" si="29"/>
+        <v>-2</v>
+      </c>
+      <c r="CX34" s="12">
+        <f t="shared" si="30"/>
+        <v>-2190.4761904700135</v>
+      </c>
+      <c r="CY34" s="11">
+        <f t="shared" si="31"/>
+        <v>-1.7228464419432103E-2</v>
+      </c>
     </row>
     <row r="35" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A35" s="14"/>
@@ -9422,10 +9941,27 @@
         <v>-1</v>
       </c>
       <c r="CS35" s="14"/>
-      <c r="CT35" s="13"/>
-      <c r="CV35" s="12"/>
-      <c r="CX35" s="12"/>
-      <c r="CY35" s="11"/>
+      <c r="CT35" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="CU35" s="10">
+        <v>2</v>
+      </c>
+      <c r="CV35" s="12">
+        <v>5314.2857142800003</v>
+      </c>
+      <c r="CW35" s="10">
+        <f t="shared" si="29"/>
+        <v>2</v>
+      </c>
+      <c r="CX35" s="12">
+        <f t="shared" si="30"/>
+        <v>5314.2857142800003</v>
+      </c>
+      <c r="CY35" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="36" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A36" s="14"/>
@@ -9673,10 +10209,22 @@
         <v>-3.5377358490566037E-2</v>
       </c>
       <c r="CS36" s="14"/>
-      <c r="CT36" s="13"/>
+      <c r="CT36" s="13" t="s">
+        <v>5</v>
+      </c>
       <c r="CV36" s="12"/>
-      <c r="CX36" s="12"/>
-      <c r="CY36" s="11"/>
+      <c r="CW36" s="10">
+        <f t="shared" si="29"/>
+        <v>-2</v>
+      </c>
+      <c r="CX36" s="12">
+        <f t="shared" si="30"/>
+        <v>-8180</v>
+      </c>
+      <c r="CY36" s="11">
+        <f t="shared" si="31"/>
+        <v>-1</v>
+      </c>
     </row>
     <row r="37" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A37" s="14"/>
@@ -9873,7 +10421,7 @@
         <v>26147.619047609998</v>
       </c>
       <c r="BY37" s="10">
-        <f t="shared" ref="BY37:BY65" si="29">BW37-BO37</f>
+        <f t="shared" ref="BY37:BY65" si="32">BW37-BO37</f>
         <v>1</v>
       </c>
       <c r="BZ37" s="12">
@@ -9929,10 +10477,22 @@
         <v>-0.44292206547357615</v>
       </c>
       <c r="CS37" s="14"/>
-      <c r="CT37" s="13"/>
+      <c r="CT37" s="13" t="s">
+        <v>4</v>
+      </c>
       <c r="CV37" s="12"/>
-      <c r="CX37" s="12"/>
-      <c r="CY37" s="11"/>
+      <c r="CW37" s="10">
+        <f t="shared" si="29"/>
+        <v>-1</v>
+      </c>
+      <c r="CX37" s="12">
+        <f t="shared" si="30"/>
+        <v>-47047.619047610002</v>
+      </c>
+      <c r="CY37" s="11">
+        <f t="shared" si="31"/>
+        <v>-1</v>
+      </c>
     </row>
     <row r="38" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A38" s="14"/>
@@ -10134,7 +10694,7 @@
         <v>154190.47619044999</v>
       </c>
       <c r="BY38" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-1</v>
       </c>
       <c r="BZ38" s="12">
@@ -10190,10 +10750,27 @@
         <v>0.36555731642900741</v>
       </c>
       <c r="CS38" s="14"/>
-      <c r="CT38" s="13"/>
-      <c r="CV38" s="12"/>
-      <c r="CX38" s="12"/>
-      <c r="CY38" s="11"/>
+      <c r="CT38" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CU38" s="10">
+        <v>7</v>
+      </c>
+      <c r="CV38" s="12">
+        <v>145523.80952379</v>
+      </c>
+      <c r="CW38" s="10">
+        <f t="shared" si="29"/>
+        <v>-7</v>
+      </c>
+      <c r="CX38" s="12">
+        <f t="shared" si="30"/>
+        <v>-100666.66666664995</v>
+      </c>
+      <c r="CY38" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.40889748549322247</v>
+      </c>
     </row>
     <row r="39" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A39" s="14"/>
@@ -10395,7 +10972,7 @@
         <v>379739.04761903</v>
       </c>
       <c r="BY39" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>4</v>
       </c>
       <c r="BZ39" s="12">
@@ -10451,10 +11028,27 @@
         <v>6.7015706806084069E-3</v>
       </c>
       <c r="CS39" s="14"/>
-      <c r="CT39" s="13"/>
-      <c r="CV39" s="12"/>
-      <c r="CX39" s="12"/>
-      <c r="CY39" s="11"/>
+      <c r="CT39" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CU39" s="10">
+        <v>21</v>
+      </c>
+      <c r="CV39" s="12">
+        <v>737020.95238092006</v>
+      </c>
+      <c r="CW39" s="10">
+        <f t="shared" si="29"/>
+        <v>8</v>
+      </c>
+      <c r="CX39" s="12">
+        <f t="shared" si="30"/>
+        <v>279211.42857142014</v>
+      </c>
+      <c r="CY39" s="11">
+        <f t="shared" si="31"/>
+        <v>0.60988558352404088</v>
+      </c>
     </row>
     <row r="40" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A40" s="9" t="s">
@@ -10657,7 +11251,7 @@
         <v>1201897.14285643</v>
       </c>
       <c r="BY40" s="27">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-1</v>
       </c>
       <c r="BZ40" s="28">
@@ -10712,13 +11306,28 @@
         <f t="shared" si="28"/>
         <v>7.7717724477374628E-2</v>
       </c>
-      <c r="CS40" s="9"/>
+      <c r="CS40" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="CT40" s="9"/>
-      <c r="CU40" s="8"/>
-      <c r="CV40" s="7"/>
-      <c r="CW40" s="27"/>
-      <c r="CX40" s="28"/>
-      <c r="CY40" s="29"/>
+      <c r="CU40" s="8">
+        <v>221</v>
+      </c>
+      <c r="CV40" s="7">
+        <v>1257073.3333327202</v>
+      </c>
+      <c r="CW40" s="27">
+        <f t="shared" si="29"/>
+        <v>8</v>
+      </c>
+      <c r="CX40" s="28">
+        <f t="shared" si="30"/>
+        <v>53265.714285630267</v>
+      </c>
+      <c r="CY40" s="29">
+        <f t="shared" si="31"/>
+        <v>4.4247696594406291E-2</v>
+      </c>
     </row>
     <row r="41" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A41" s="14">
@@ -10920,7 +11529,7 @@
       </c>
       <c r="BX41" s="33"/>
       <c r="BY41" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-543</v>
       </c>
       <c r="BZ41" s="12">
@@ -10975,13 +11584,28 @@
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CS41" s="14"/>
-      <c r="CT41" s="32"/>
-      <c r="CU41" s="15"/>
+      <c r="CS41" s="14">
+        <v>81</v>
+      </c>
+      <c r="CT41" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CU41" s="15">
+        <v>1229</v>
+      </c>
       <c r="CV41" s="33"/>
-      <c r="CW41" s="10"/>
-      <c r="CX41" s="12"/>
-      <c r="CY41" s="11"/>
+      <c r="CW41" s="10">
+        <f t="shared" si="29"/>
+        <v>-94</v>
+      </c>
+      <c r="CX41" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY41" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="42" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A42" s="14"/>
@@ -11163,7 +11787,7 @@
       </c>
       <c r="BX42" s="33"/>
       <c r="BY42" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-4</v>
       </c>
       <c r="BZ42" s="12">
@@ -11198,11 +11822,13 @@
       <c r="CL42" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CM42" s="15"/>
+      <c r="CM42" s="15">
+        <v>6</v>
+      </c>
       <c r="CN42" s="33"/>
       <c r="CO42" s="10">
         <f t="shared" si="26"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="CP42" s="12">
         <f t="shared" si="27"/>
@@ -11213,12 +11839,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CS42" s="14"/>
-      <c r="CT42" s="32"/>
+      <c r="CT42" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CU42" s="15"/>
       <c r="CV42" s="33"/>
-      <c r="CW42" s="10"/>
-      <c r="CX42" s="12"/>
-      <c r="CY42" s="11"/>
+      <c r="CW42" s="10">
+        <f t="shared" si="29"/>
+        <v>-6</v>
+      </c>
+      <c r="CX42" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY42" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="43" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A43" s="14"/>
@@ -11420,7 +12057,7 @@
         <v>82412.380952079999</v>
       </c>
       <c r="BY43" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-55</v>
       </c>
       <c r="BZ43" s="12">
@@ -11476,10 +12113,27 @@
         <v>4.4907046644309105E-2</v>
       </c>
       <c r="CS43" s="14"/>
-      <c r="CT43" s="13"/>
-      <c r="CV43" s="12"/>
-      <c r="CX43" s="12"/>
-      <c r="CY43" s="11"/>
+      <c r="CT43" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CU43" s="10">
+        <v>96</v>
+      </c>
+      <c r="CV43" s="12">
+        <v>85103.809523370001</v>
+      </c>
+      <c r="CW43" s="10">
+        <f t="shared" si="29"/>
+        <v>-2</v>
+      </c>
+      <c r="CX43" s="12">
+        <f t="shared" si="30"/>
+        <v>-4290.4761905000341</v>
+      </c>
+      <c r="CY43" s="11">
+        <f t="shared" si="31"/>
+        <v>-4.7994971448542402E-2</v>
+      </c>
     </row>
     <row r="44" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A44" s="14"/>
@@ -11681,7 +12335,7 @@
         <v>90152.380952249994</v>
       </c>
       <c r="BY44" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>3</v>
       </c>
       <c r="BZ44" s="12">
@@ -11737,10 +12391,27 @@
         <v>-0.25631621841911384</v>
       </c>
       <c r="CS44" s="14"/>
-      <c r="CT44" s="13"/>
-      <c r="CV44" s="12"/>
-      <c r="CX44" s="12"/>
-      <c r="CY44" s="11"/>
+      <c r="CT44" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CU44" s="10">
+        <v>61</v>
+      </c>
+      <c r="CV44" s="12">
+        <v>57428.571428510018</v>
+      </c>
+      <c r="CW44" s="10">
+        <f t="shared" si="29"/>
+        <v>-14</v>
+      </c>
+      <c r="CX44" s="12">
+        <f t="shared" si="30"/>
+        <v>-8619.0476190099798</v>
+      </c>
+      <c r="CY44" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.13049747656775848</v>
+      </c>
     </row>
     <row r="45" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A45" s="14"/>
@@ -11942,7 +12613,7 @@
         <v>92723.80952380001</v>
       </c>
       <c r="BY45" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-2</v>
       </c>
       <c r="BZ45" s="12">
@@ -11998,10 +12669,27 @@
         <v>-0.54991257786034653</v>
       </c>
       <c r="CS45" s="14"/>
-      <c r="CT45" s="13"/>
-      <c r="CV45" s="12"/>
-      <c r="CX45" s="12"/>
-      <c r="CY45" s="11"/>
+      <c r="CT45" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CU45" s="10">
+        <v>12</v>
+      </c>
+      <c r="CV45" s="12">
+        <v>84647.619047610002</v>
+      </c>
+      <c r="CW45" s="10">
+        <f t="shared" si="29"/>
+        <v>2</v>
+      </c>
+      <c r="CX45" s="12">
+        <f t="shared" si="30"/>
+        <v>21885.714285710004</v>
+      </c>
+      <c r="CY45" s="11">
+        <f t="shared" si="31"/>
+        <v>0.34871016691953338</v>
+      </c>
     </row>
     <row r="46" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A46" s="14"/>
@@ -12203,7 +12891,7 @@
         <v>111428.57142854</v>
       </c>
       <c r="BY46" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>2</v>
       </c>
       <c r="BZ46" s="12">
@@ -12259,10 +12947,27 @@
         <v>-0.26202661207776362</v>
       </c>
       <c r="CS46" s="14"/>
-      <c r="CT46" s="13"/>
-      <c r="CV46" s="12"/>
-      <c r="CX46" s="12"/>
-      <c r="CY46" s="11"/>
+      <c r="CT46" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CU46" s="10">
+        <v>13</v>
+      </c>
+      <c r="CV46" s="12">
+        <v>130190.47619044001</v>
+      </c>
+      <c r="CW46" s="10">
+        <f t="shared" si="29"/>
+        <v>5</v>
+      </c>
+      <c r="CX46" s="12">
+        <f t="shared" si="30"/>
+        <v>-7142.8571428699943</v>
+      </c>
+      <c r="CY46" s="11">
+        <f t="shared" si="31"/>
+        <v>-5.2011095700518505E-2</v>
+      </c>
     </row>
     <row r="47" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A47" s="14"/>
@@ -12444,7 +13149,7 @@
       </c>
       <c r="BX47" s="12"/>
       <c r="BY47" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BZ47" s="12">
@@ -12490,10 +13195,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CS47" s="14"/>
-      <c r="CT47" s="13"/>
+      <c r="CT47" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="CV47" s="12"/>
-      <c r="CX47" s="12"/>
-      <c r="CY47" s="11"/>
+      <c r="CW47" s="10">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="CX47" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY47" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="48" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A48" s="14"/>
@@ -12695,7 +13412,7 @@
         <v>6290</v>
       </c>
       <c r="BY48" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-1</v>
       </c>
       <c r="BZ48" s="12">
@@ -12751,10 +13468,22 @@
         <v>0.31729518855656696</v>
       </c>
       <c r="CS48" s="14"/>
-      <c r="CT48" s="13"/>
+      <c r="CT48" s="13" t="s">
+        <v>5</v>
+      </c>
       <c r="CV48" s="12"/>
-      <c r="CX48" s="12"/>
-      <c r="CY48" s="11"/>
+      <c r="CW48" s="10">
+        <f t="shared" si="29"/>
+        <v>-4</v>
+      </c>
+      <c r="CX48" s="12">
+        <f t="shared" si="30"/>
+        <v>-20260</v>
+      </c>
+      <c r="CY48" s="11">
+        <f t="shared" si="31"/>
+        <v>-1</v>
+      </c>
     </row>
     <row r="49" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A49" s="14"/>
@@ -12956,7 +13685,7 @@
         <v>52168.571428559997</v>
       </c>
       <c r="BY49" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-1</v>
       </c>
       <c r="BZ49" s="12">
@@ -13007,10 +13736,27 @@
         <v>-1</v>
       </c>
       <c r="CS49" s="14"/>
-      <c r="CT49" s="13"/>
-      <c r="CV49" s="12"/>
-      <c r="CX49" s="12"/>
-      <c r="CY49" s="11"/>
+      <c r="CT49" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CU49" s="10">
+        <v>1</v>
+      </c>
+      <c r="CV49" s="12">
+        <v>25619.04761904</v>
+      </c>
+      <c r="CW49" s="10">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="CX49" s="12">
+        <f t="shared" si="30"/>
+        <v>25619.04761904</v>
+      </c>
+      <c r="CY49" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="50" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A50" s="14"/>
@@ -13212,7 +13958,7 @@
         <v>166761.90476188</v>
       </c>
       <c r="BY50" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-6</v>
       </c>
       <c r="BZ50" s="12">
@@ -13268,10 +14014,27 @@
         <v>-0.56665160415729177</v>
       </c>
       <c r="CS50" s="14"/>
-      <c r="CT50" s="13"/>
-      <c r="CV50" s="12"/>
-      <c r="CX50" s="12"/>
-      <c r="CY50" s="11"/>
+      <c r="CT50" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CU50" s="10">
+        <v>11</v>
+      </c>
+      <c r="CV50" s="12">
+        <v>191142.85714283001</v>
+      </c>
+      <c r="CW50" s="10">
+        <f t="shared" si="29"/>
+        <v>4</v>
+      </c>
+      <c r="CX50" s="12">
+        <f t="shared" si="30"/>
+        <v>99809.523809520004</v>
+      </c>
+      <c r="CY50" s="11">
+        <f t="shared" si="31"/>
+        <v>1.0928050052140019</v>
+      </c>
     </row>
     <row r="51" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A51" s="14"/>
@@ -13473,7 +14236,7 @@
         <v>370285.7142857</v>
       </c>
       <c r="BY51" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-12</v>
       </c>
       <c r="BZ51" s="12">
@@ -13529,10 +14292,27 @@
         <v>-0.12698139214333357</v>
       </c>
       <c r="CS51" s="14"/>
-      <c r="CT51" s="13"/>
-      <c r="CV51" s="12"/>
-      <c r="CX51" s="12"/>
-      <c r="CY51" s="11"/>
+      <c r="CT51" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CU51" s="10">
+        <v>24</v>
+      </c>
+      <c r="CV51" s="12">
+        <v>868190.47619043</v>
+      </c>
+      <c r="CW51" s="10">
+        <f t="shared" si="29"/>
+        <v>-2</v>
+      </c>
+      <c r="CX51" s="12">
+        <f t="shared" si="30"/>
+        <v>-96952.380952410051</v>
+      </c>
+      <c r="CY51" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.10045391750545921</v>
+      </c>
     </row>
     <row r="52" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A52" s="9" t="s">
@@ -13735,7 +14515,7 @@
         <v>972223.33333280997</v>
       </c>
       <c r="BY52" s="27">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-72</v>
       </c>
       <c r="BZ52" s="28">
@@ -13790,13 +14570,28 @@
         <f t="shared" si="28"/>
         <v>-0.30440137946095486</v>
       </c>
-      <c r="CS52" s="9"/>
+      <c r="CS52" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="CT52" s="9"/>
-      <c r="CU52" s="8"/>
-      <c r="CV52" s="7"/>
-      <c r="CW52" s="27"/>
-      <c r="CX52" s="28"/>
-      <c r="CY52" s="29"/>
+      <c r="CU52" s="8">
+        <v>218</v>
+      </c>
+      <c r="CV52" s="7">
+        <v>1442322.85714223</v>
+      </c>
+      <c r="CW52" s="27">
+        <f t="shared" si="29"/>
+        <v>-10</v>
+      </c>
+      <c r="CX52" s="28">
+        <f t="shared" si="30"/>
+        <v>10049.523809480015</v>
+      </c>
+      <c r="CY52" s="29">
+        <f t="shared" si="31"/>
+        <v>7.016484616170173E-3</v>
+      </c>
     </row>
     <row r="53" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A53" s="14">
@@ -13970,7 +14765,7 @@
       <c r="BW53" s="15"/>
       <c r="BX53" s="33"/>
       <c r="BY53" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BZ53" s="12">
@@ -14021,13 +14816,26 @@
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CS53" s="14"/>
-      <c r="CT53" s="32"/>
+      <c r="CS53" s="14">
+        <v>84</v>
+      </c>
+      <c r="CT53" s="32" t="s">
+        <v>20</v>
+      </c>
       <c r="CU53" s="15"/>
       <c r="CV53" s="33"/>
-      <c r="CW53" s="10"/>
-      <c r="CX53" s="12"/>
-      <c r="CY53" s="11"/>
+      <c r="CW53" s="10">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="CX53" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY53" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="54" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A54" s="14"/>
@@ -14209,7 +15017,7 @@
       </c>
       <c r="BX54" s="33"/>
       <c r="BY54" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-3</v>
       </c>
       <c r="BZ54" s="12">
@@ -14224,7 +15032,9 @@
       <c r="CD54" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CE54" s="15"/>
+      <c r="CE54" s="15">
+        <v>0</v>
+      </c>
       <c r="CF54" s="33"/>
       <c r="CG54" s="10">
         <f t="shared" si="23"/>
@@ -14242,11 +15052,13 @@
       <c r="CL54" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CM54" s="15"/>
+      <c r="CM54" s="15">
+        <v>2</v>
+      </c>
       <c r="CN54" s="33"/>
       <c r="CO54" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CP54" s="12">
         <f t="shared" si="27"/>
@@ -14257,12 +15069,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CS54" s="14"/>
-      <c r="CT54" s="32"/>
+      <c r="CT54" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CU54" s="15"/>
       <c r="CV54" s="33"/>
-      <c r="CW54" s="10"/>
-      <c r="CX54" s="12"/>
-      <c r="CY54" s="11"/>
+      <c r="CW54" s="10">
+        <f t="shared" si="29"/>
+        <v>-2</v>
+      </c>
+      <c r="CX54" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY54" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="55" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A55" s="14"/>
@@ -14464,7 +15287,7 @@
         <v>102147.61904713005</v>
       </c>
       <c r="BY55" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-32</v>
       </c>
       <c r="BZ55" s="12">
@@ -14520,10 +15343,27 @@
         <v>-0.33098276342556177</v>
       </c>
       <c r="CS55" s="14"/>
-      <c r="CT55" s="13"/>
-      <c r="CV55" s="12"/>
-      <c r="CX55" s="12"/>
-      <c r="CY55" s="11"/>
+      <c r="CT55" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CU55" s="10">
+        <v>86</v>
+      </c>
+      <c r="CV55" s="12">
+        <v>90476.190475840005</v>
+      </c>
+      <c r="CW55" s="10">
+        <f t="shared" si="29"/>
+        <v>11</v>
+      </c>
+      <c r="CX55" s="12">
+        <f t="shared" si="30"/>
+        <v>15029.52380948003</v>
+      </c>
+      <c r="CY55" s="11">
+        <f t="shared" si="31"/>
+        <v>0.1992072608846133</v>
+      </c>
     </row>
     <row r="56" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A56" s="14"/>
@@ -14725,7 +15565,7 @@
         <v>100334.28571419</v>
       </c>
       <c r="BY56" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-15</v>
       </c>
       <c r="BZ56" s="12">
@@ -14781,10 +15621,27 @@
         <v>-0.12004405286396851</v>
       </c>
       <c r="CS56" s="14"/>
-      <c r="CT56" s="13"/>
-      <c r="CV56" s="12"/>
-      <c r="CX56" s="12"/>
-      <c r="CY56" s="11"/>
+      <c r="CT56" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CU56" s="10">
+        <v>78</v>
+      </c>
+      <c r="CV56" s="12">
+        <v>79542.857142770008</v>
+      </c>
+      <c r="CW56" s="10">
+        <f t="shared" si="29"/>
+        <v>19</v>
+      </c>
+      <c r="CX56" s="12">
+        <f t="shared" si="30"/>
+        <v>11057.142857160012</v>
+      </c>
+      <c r="CY56" s="11">
+        <f t="shared" si="31"/>
+        <v>0.16145181476895692</v>
+      </c>
     </row>
     <row r="57" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A57" s="14"/>
@@ -14986,7 +15843,7 @@
         <v>131247.61904760002</v>
       </c>
       <c r="BY57" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-7</v>
       </c>
       <c r="BZ57" s="12">
@@ -15042,10 +15899,27 @@
         <v>-0.5663554715197523</v>
       </c>
       <c r="CS57" s="14"/>
-      <c r="CT57" s="13"/>
-      <c r="CV57" s="12"/>
-      <c r="CX57" s="12"/>
-      <c r="CY57" s="11"/>
+      <c r="CT57" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CU57" s="10">
+        <v>10</v>
+      </c>
+      <c r="CV57" s="12">
+        <v>67047.619047610002</v>
+      </c>
+      <c r="CW57" s="10">
+        <f t="shared" si="29"/>
+        <v>-1</v>
+      </c>
+      <c r="CX57" s="12">
+        <f t="shared" si="30"/>
+        <v>-2847.619047619999</v>
+      </c>
+      <c r="CY57" s="11">
+        <f t="shared" si="31"/>
+        <v>-4.0741245401299156E-2</v>
+      </c>
     </row>
     <row r="58" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A58" s="14"/>
@@ -15247,7 +16121,7 @@
         <v>42476.190476169999</v>
       </c>
       <c r="BY58" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-11</v>
       </c>
       <c r="BZ58" s="12">
@@ -15303,10 +16177,27 @@
         <v>-7.6998050682191982E-2</v>
       </c>
       <c r="CS58" s="14"/>
-      <c r="CT58" s="13"/>
-      <c r="CV58" s="12"/>
-      <c r="CX58" s="12"/>
-      <c r="CY58" s="11"/>
+      <c r="CT58" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CU58" s="10">
+        <v>8</v>
+      </c>
+      <c r="CV58" s="12">
+        <v>98285.714285690003</v>
+      </c>
+      <c r="CW58" s="10">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="CX58" s="12">
+        <f t="shared" si="30"/>
+        <v>8095.2380952400126</v>
+      </c>
+      <c r="CY58" s="11">
+        <f t="shared" si="31"/>
+        <v>8.9757127771958628E-2</v>
+      </c>
     </row>
     <row r="59" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A59" s="14"/>
@@ -15483,7 +16374,7 @@
       </c>
       <c r="BX59" s="12"/>
       <c r="BY59" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BZ59" s="12">
@@ -15529,10 +16420,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CS59" s="14"/>
-      <c r="CT59" s="13"/>
+      <c r="CT59" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="CV59" s="12"/>
-      <c r="CX59" s="12"/>
-      <c r="CY59" s="11"/>
+      <c r="CW59" s="10">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="CX59" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY59" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="60" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A60" s="14"/>
@@ -15729,7 +16632,7 @@
         <v>6290</v>
       </c>
       <c r="BY60" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="BZ60" s="12">
@@ -15780,10 +16683,22 @@
         <v>-1</v>
       </c>
       <c r="CS60" s="14"/>
-      <c r="CT60" s="13"/>
+      <c r="CT60" s="13" t="s">
+        <v>5</v>
+      </c>
       <c r="CV60" s="12"/>
-      <c r="CX60" s="12"/>
-      <c r="CY60" s="11"/>
+      <c r="CW60" s="10">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="CX60" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY60" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="61" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A61" s="14"/>
@@ -15985,7 +16900,7 @@
         <v>83142.857142840003</v>
       </c>
       <c r="BY61" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-3</v>
       </c>
       <c r="BZ61" s="12">
@@ -16041,10 +16956,27 @@
         <v>-0.69801462904915956</v>
       </c>
       <c r="CS61" s="14"/>
-      <c r="CT61" s="13"/>
-      <c r="CV61" s="12"/>
-      <c r="CX61" s="12"/>
-      <c r="CY61" s="11"/>
+      <c r="CT61" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CU61" s="10">
+        <v>2</v>
+      </c>
+      <c r="CV61" s="12">
+        <v>96952.380952370004</v>
+      </c>
+      <c r="CW61" s="10">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="CX61" s="12">
+        <f t="shared" si="30"/>
+        <v>69428.571428570009</v>
+      </c>
+      <c r="CY61" s="11">
+        <f t="shared" si="31"/>
+        <v>2.5224913494817902</v>
+      </c>
     </row>
     <row r="62" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A62" s="14"/>
@@ -16246,7 +17178,7 @@
         <v>217142.85714284002</v>
       </c>
       <c r="BY62" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-6</v>
       </c>
       <c r="BZ62" s="12">
@@ -16302,10 +17234,27 @@
         <v>-0.76013006503255576</v>
       </c>
       <c r="CS62" s="14"/>
-      <c r="CT62" s="13"/>
-      <c r="CV62" s="12"/>
-      <c r="CX62" s="12"/>
-      <c r="CY62" s="11"/>
+      <c r="CT62" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CU62" s="10">
+        <v>6</v>
+      </c>
+      <c r="CV62" s="12">
+        <v>83974.285714259997</v>
+      </c>
+      <c r="CW62" s="10">
+        <f t="shared" si="29"/>
+        <v>-1</v>
+      </c>
+      <c r="CX62" s="12">
+        <f t="shared" si="30"/>
+        <v>-7359.0476190500049</v>
+      </c>
+      <c r="CY62" s="11">
+        <f t="shared" si="31"/>
+        <v>-8.0573514077210417E-2</v>
+      </c>
     </row>
     <row r="63" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A63" s="14"/>
@@ -16507,7 +17456,7 @@
         <v>456340.95238093007</v>
       </c>
       <c r="BY63" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-9</v>
       </c>
       <c r="BZ63" s="12">
@@ -16563,10 +17512,27 @@
         <v>0.12483745123538241</v>
       </c>
       <c r="CS63" s="14"/>
-      <c r="CT63" s="13"/>
-      <c r="CV63" s="12"/>
-      <c r="CX63" s="12"/>
-      <c r="CY63" s="11"/>
+      <c r="CT63" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CU63" s="10">
+        <v>15</v>
+      </c>
+      <c r="CV63" s="12">
+        <v>526812.38095234998</v>
+      </c>
+      <c r="CW63" s="10">
+        <f t="shared" si="29"/>
+        <v>-5</v>
+      </c>
+      <c r="CX63" s="12">
+        <f t="shared" si="30"/>
+        <v>-132235.23809524009</v>
+      </c>
+      <c r="CY63" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.20064595375723729</v>
+      </c>
     </row>
     <row r="64" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A64" s="9" t="s">
@@ -16769,7 +17735,7 @@
         <v>1139122.3809517003</v>
       </c>
       <c r="BY64" s="27">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-82</v>
       </c>
       <c r="BZ64" s="28">
@@ -16824,13 +17790,28 @@
         <f t="shared" si="28"/>
         <v>-0.28637091758853916</v>
       </c>
-      <c r="CS64" s="9"/>
+      <c r="CS64" s="9" t="s">
+        <v>1</v>
+      </c>
       <c r="CT64" s="9"/>
-      <c r="CU64" s="8"/>
-      <c r="CV64" s="7"/>
-      <c r="CW64" s="27"/>
-      <c r="CX64" s="28"/>
-      <c r="CY64" s="29"/>
+      <c r="CU64" s="8">
+        <v>205</v>
+      </c>
+      <c r="CV64" s="7">
+        <v>1043091.4285708901</v>
+      </c>
+      <c r="CW64" s="27">
+        <f t="shared" si="29"/>
+        <v>24</v>
+      </c>
+      <c r="CX64" s="28">
+        <f t="shared" si="30"/>
+        <v>-38831.42857146007</v>
+      </c>
+      <c r="CY64" s="29">
+        <f t="shared" si="31"/>
+        <v>-3.5891125060454256E-2</v>
+      </c>
     </row>
     <row r="65" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A65" s="4" t="s">
@@ -17033,7 +18014,7 @@
         <v>11122184.761900868</v>
       </c>
       <c r="BY65" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-669</v>
       </c>
       <c r="BZ65" s="5">
@@ -17088,13 +18069,28 @@
         <f t="shared" si="28"/>
         <v>-0.10400049951712022</v>
       </c>
-      <c r="CS65" s="4"/>
+      <c r="CS65" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="CT65" s="4"/>
-      <c r="CU65" s="3"/>
-      <c r="CV65" s="2"/>
-      <c r="CW65" s="6"/>
-      <c r="CX65" s="5"/>
-      <c r="CY65" s="30"/>
+      <c r="CU65" s="3">
+        <v>2238</v>
+      </c>
+      <c r="CV65" s="2">
+        <v>27538164.761900596</v>
+      </c>
+      <c r="CW65" s="6">
+        <f t="shared" si="29"/>
+        <v>178</v>
+      </c>
+      <c r="CX65" s="5">
+        <f t="shared" si="30"/>
+        <v>8398197.6190473996</v>
+      </c>
+      <c r="CY65" s="30">
+        <f t="shared" si="31"/>
+        <v>0.43877805830942923</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -17104,7 +18100,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="110" operator="containsText" id="{84E91190-11E8-AE4A-9A8E-E0B241655290}">
+          <x14:cfRule type="containsText" priority="111" operator="containsText" id="{84E91190-11E8-AE4A-9A8E-E0B241655290}">
             <xm:f>NOT(ISERROR(SEARCH("-",E7)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17116,7 +18112,7 @@
           <xm:sqref>E7:G65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{CCFCC0A6-CB12-AB49-93FE-0A85BBD26278}">
+          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{CCFCC0A6-CB12-AB49-93FE-0A85BBD26278}">
             <xm:f>NOT(ISERROR(SEARCH("-",M5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17128,7 +18124,7 @@
           <xm:sqref>M5:O65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{77E3898A-1BFA-D640-9BA9-3433EFE4A95F}">
+          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{77E3898A-1BFA-D640-9BA9-3433EFE4A95F}">
             <xm:f>NOT(ISERROR(SEARCH("-",U5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17140,7 +18136,7 @@
           <xm:sqref>U5:W65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{D9706009-D5AD-2741-B804-EFED1C726C5E}">
+          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{D9706009-D5AD-2741-B804-EFED1C726C5E}">
             <xm:f>NOT(ISERROR(SEARCH("-",AC5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17152,7 +18148,7 @@
           <xm:sqref>AC5:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{0ED7C4E6-BDE3-3246-BC08-84A539C7A360}">
+          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{0ED7C4E6-BDE3-3246-BC08-84A539C7A360}">
             <xm:f>NOT(ISERROR(SEARCH("-",AJ5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17164,7 +18160,7 @@
           <xm:sqref>AJ5:AM65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{6F25B2E1-166C-A14E-8434-CB8394590228}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{6F25B2E1-166C-A14E-8434-CB8394590228}">
             <xm:f>NOT(ISERROR(SEARCH("-",AS5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17176,7 +18172,7 @@
           <xm:sqref>AS5:AU65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{B91A5596-3F8E-6648-95BA-8781A9ECC29E}">
+          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{B91A5596-3F8E-6648-95BA-8781A9ECC29E}">
             <xm:f>NOT(ISERROR(SEARCH("-",BA5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17188,7 +18184,7 @@
           <xm:sqref>BA5:BC65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{E93B6814-05C6-8F46-A383-0AA3B037BA87}">
+          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{E93B6814-05C6-8F46-A383-0AA3B037BA87}">
             <xm:f>NOT(ISERROR(SEARCH("-",BI5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17200,7 +18196,7 @@
           <xm:sqref>BI5:BK65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{C5C117FA-A310-C347-B988-7B736BE0F8CB}">
+          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{C5C117FA-A310-C347-B988-7B736BE0F8CB}">
             <xm:f>NOT(ISERROR(SEARCH("-",BQ5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17212,7 +18208,7 @@
           <xm:sqref>BQ5:BS65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{8AD91545-A880-0646-B88D-4021F4CD6A07}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{8AD91545-A880-0646-B88D-4021F4CD6A07}">
             <xm:f>NOT(ISERROR(SEARCH("-",BY5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17224,7 +18220,7 @@
           <xm:sqref>BY5:CA65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{6A1FAD57-8B56-AD43-BC86-FE7B8B27DAC3}">
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{6A1FAD57-8B56-AD43-BC86-FE7B8B27DAC3}">
             <xm:f>NOT(ISERROR(SEARCH("-",CG5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17236,7 +18232,7 @@
           <xm:sqref>CG5:CI65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{F04093BB-F5FD-F043-B0A6-2D2AB47A2695}">
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{F04093BB-F5FD-F043-B0A6-2D2AB47A2695}">
             <xm:f>NOT(ISERROR(SEARCH("-",CO5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17248,7 +18244,7 @@
           <xm:sqref>CO5:CQ65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{4126E041-CCDA-FB44-8F91-ACB733D36FB3}">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{3F8775C0-1F6C-794D-A1A7-74CBBEDF3DB8}">
             <xm:f>NOT(ISERROR(SEARCH("-",CW5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
